--- a/tame_output/ON/bt/strategyON_20240608.xlsx
+++ b/tame_output/ON/bt/strategyON_20240608.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>45.8%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.8%</t>
+          <t>-80.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.7%</t>
+          <t>108.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>87.3%</t>
+          <t>87.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.4%</t>
+          <t>-77.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.1%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>452.7%</t>
+          <t>452.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-689.4%</t>
+          <t>-682.3%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-28.9%</t>
+          <t>-29.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-298.8%</t>
+          <t>-295.9%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-31.0%</t>
+          <t>-30.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-25.1%</t>
+          <t>-24.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-273.3%</t>
+          <t>-266.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-187.0%</t>
+          <t>-182.8%</t>
         </is>
       </c>
     </row>
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.737904856647299</v>
+        <v>3.738918947566699</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-5.278230276605696</v>
+        <v>-5.207695458748025</v>
       </c>
       <c r="E1988" t="n">
-        <v>0.7745118885346867</v>
+        <v>0.8027258156777553</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.493398669565592</v>
+        <v>-0.4228638517079198</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.590121221751358</v>
+        <v>2.632442112465961</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240608.xlsx
+++ b/tame_output/ON/bt/strategyON_20240608.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>48.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>69.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>18.4%</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.6%</t>
+          <t>-81.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.8%</t>
+          <t>108.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>128.3%</t>
+          <t>128.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>87.6%</t>
+          <t>86.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.1%</t>
+          <t>-78.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>89.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>452.8%</t>
+          <t>449.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.4%</t>
+          <t>-10.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-682.3%</t>
+          <t>-710.4%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-29.3%</t>
+          <t>-28.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-295.9%</t>
+          <t>-307.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-30.2%</t>
+          <t>-31.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-24.0%</t>
+          <t>-25.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-266.3%</t>
+          <t>-273.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>33.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-16.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-182.8%</t>
+          <t>-187.0%</t>
         </is>
       </c>
     </row>
@@ -46148,10 +46148,10 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-5.081422609279906</v>
+        <v>-5.291184324387523</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.7970011637386496</v>
+        <v>0.7130964776956032</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.4526509157185012</v>
@@ -46171,10 +46171,10 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-5.192358861921155</v>
+        <v>-5.402120577028771</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.7283686914433569</v>
+        <v>0.6444640054003106</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.4526509157185012</v>
@@ -46194,10 +46194,10 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.395385439464389</v>
+        <v>-5.605147154572005</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.6502894456459694</v>
+        <v>0.566384759602923</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.6556774932617346</v>
@@ -46217,10 +46217,10 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-5.237459840529096</v>
+        <v>-5.447221555636712</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.7236320716522191</v>
+        <v>0.6397273856091723</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.6556774932617346</v>
@@ -46240,10 +46240,10 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-5.151216377502718</v>
+        <v>-5.360978092610334</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.7530757274366304</v>
+        <v>0.6691710413935841</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.6556774932617346</v>
@@ -46263,10 +46263,10 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-5.196523196901698</v>
+        <v>-5.406284912009314</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.7267287751215639</v>
+        <v>0.6428240890785175</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.6964876562709654</v>
@@ -46286,10 +46286,10 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-5.225556301603999</v>
+        <v>-5.435318016711615</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.7156674062737451</v>
+        <v>0.6317627202306988</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.6964876562709654</v>
@@ -46309,10 +46309,10 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-5.132745820153139</v>
+        <v>-5.342507535260755</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.6820642907454544</v>
+        <v>0.598159604702408</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.6036771748201061</v>
@@ -46332,10 +46332,10 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-5.177135289482567</v>
+        <v>-5.386897004590183</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.6661819789382846</v>
+        <v>0.5822772928952378</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.6480666441495337</v>
@@ -46355,10 +46355,10 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-5.064464071246316</v>
+        <v>-5.274225786353933</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.7063261747445075</v>
+        <v>0.6224214887014612</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.5353954259132836</v>
@@ -46378,10 +46378,10 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.952087070063643</v>
+        <v>-5.16184878517126</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.756768271048244</v>
+        <v>0.6728635850051976</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.5353954259132836</v>
@@ -46401,10 +46401,10 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-5.150321638950374</v>
+        <v>-5.36008335405799</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.6889716452620904</v>
+        <v>0.6050669592190441</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.7336299948000142</v>
@@ -46424,10 +46424,10 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-5.233322919975653</v>
+        <v>-5.443084635083269</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.4941268528526321</v>
+        <v>0.4102221668095858</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.7522008793271879</v>
@@ -46447,10 +46447,10 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-5.341936998418984</v>
+        <v>-5.5516987135266</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.5708308821945054</v>
+        <v>0.486926196151459</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.7522008793271879</v>
@@ -46470,10 +46470,10 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.428535581400087</v>
+        <v>-5.638297296507703</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.5507044751043875</v>
+        <v>0.4667997890613407</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.7522008793271879</v>
@@ -46493,10 +46493,10 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.390151918841936</v>
+        <v>-5.599913633949552</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.5634773814700162</v>
+        <v>0.4795726954269699</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.7138172167690368</v>
@@ -46516,10 +46516,10 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-5.21303558880677</v>
+        <v>-5.422797303914386</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.6310529423293847</v>
+        <v>0.5471482562863383</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.7138172167690368</v>
@@ -46539,10 +46539,10 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-5.258127833640316</v>
+        <v>-5.467889548747932</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.6136994361578796</v>
+        <v>0.5297947501148332</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.7757132599384265</v>
@@ -46562,10 +46562,10 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-5.078752412401548</v>
+        <v>-5.288514127509164</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.679236579959801</v>
+        <v>0.5953318939167547</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.6189365017677079</v>
@@ -46585,10 +46585,10 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-5.123766625922155</v>
+        <v>-5.333528341029771</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.6420383498831481</v>
+        <v>0.5581336638401018</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.6492853970823125</v>
@@ -46608,10 +46608,10 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.39077113619459</v>
+        <v>-5.600532851302206</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.5409281081131199</v>
+        <v>0.4570234220700735</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.8436484351252611</v>
@@ -46631,10 +46631,10 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.491968917631763</v>
+        <v>-5.701730632739379</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.4996529174347524</v>
+        <v>0.4157482313917056</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.9120572486705802</v>
@@ -46654,10 +46654,10 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.45949333146099</v>
+        <v>-5.669255046568606</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.5102431134573777</v>
+        <v>0.4263384274143314</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.9120572486705802</v>
@@ -46677,10 +46677,10 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.440455203753693</v>
+        <v>-5.650216918861309</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.5143830837485415</v>
+        <v>0.4304783977054951</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.9702408600017748</v>
@@ -46700,10 +46700,10 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.471581834904311</v>
+        <v>-5.681343550011928</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.679514300226975</v>
+        <v>0.5956096141839282</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.9702408600017748</v>
@@ -46723,10 +46723,10 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.523902215505103</v>
+        <v>-5.733663930612719</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.6594194769727917</v>
+        <v>0.5755147909297453</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.9352939999929026</v>
@@ -46746,10 +46746,10 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.544159514034061</v>
+        <v>-5.753921229141677</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.6573250879581343</v>
+        <v>0.5734204019150879</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.9352939999929026</v>
@@ -46769,10 +46769,10 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.396416543799059</v>
+        <v>-5.606178258906675</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.7955749238441574</v>
+        <v>0.711670237801111</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.7674866427580195</v>
@@ -46792,10 +46792,10 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.49843122633028</v>
+        <v>-5.708192941437896</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.7575626723631497</v>
+        <v>0.6736579863201033</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.7674866427580195</v>
@@ -46815,10 +46815,10 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.361821882236187</v>
+        <v>-5.571583597343803</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8128687583924452</v>
+        <v>0.7289640723493989</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.6308772986639271</v>
@@ -46838,10 +46838,10 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.504587215058837</v>
+        <v>-5.714348930166453</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.7548431020034956</v>
+        <v>0.6709384159604492</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.7736426314865774</v>
@@ -46861,10 +46861,10 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.442289216282715</v>
+        <v>-5.652050931390331</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.8460978553107652</v>
+        <v>0.7621931692677189</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.7736426314865774</v>
@@ -46884,10 +46884,10 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-5.240499018617557</v>
+        <v>-5.450260733725173</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.6353948067662265</v>
+        <v>0.5514901207231802</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.575624439317423</v>
@@ -46907,10 +46907,10 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-5.180608336974964</v>
+        <v>-5.39037005208258</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.7296413117454392</v>
+        <v>0.6457366257023924</v>
       </c>
       <c r="F1972" t="n">
         <v>-0.5157337576748295</v>
@@ -46930,10 +46930,10 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.278348881599938</v>
+        <v>-5.488110596707554</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.705172830011493</v>
+        <v>0.6212681439684467</v>
       </c>
       <c r="F1973" t="n">
         <v>-0.5316230358078098</v>
@@ -46953,10 +46953,10 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.454686641722867</v>
+        <v>-5.664448356830484</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.6331737067869927</v>
+        <v>0.5492690207439463</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.7079607959307392</v>
@@ -46976,10 +46976,10 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.453997269561644</v>
+        <v>-5.66375898466926</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.6319410736914106</v>
+        <v>0.5480363876483643</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.7079607959307392</v>
@@ -46999,10 +46999,10 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.460568234616237</v>
+        <v>-5.670329949723853</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.62917555510501</v>
+        <v>0.5452708690619632</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.7145317609853321</v>
@@ -47022,10 +47022,10 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.452614264321465</v>
+        <v>-5.662375979429081</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.6323571432229187</v>
+        <v>0.5484524571798723</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.7145317609853321</v>
@@ -47045,10 +47045,10 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.442240887988378</v>
+        <v>-5.652002603095994</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.6428882507839582</v>
+        <v>0.5589835647409118</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.7041583846522448</v>
@@ -47068,10 +47068,10 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-5.314556578194082</v>
+        <v>-5.524318293301698</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.6988543480764013</v>
+        <v>0.614949662033355</v>
       </c>
       <c r="F1979" t="n">
         <v>-0.5764740748579483</v>
@@ -47091,10 +47091,10 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.37522316859647</v>
+        <v>-5.584984883704086</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.6613423843913182</v>
+        <v>0.5774376983482719</v>
       </c>
       <c r="F1980" t="n">
         <v>-0.658172391576482</v>
@@ -47114,10 +47114,10 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-5.310229308662825</v>
+        <v>-5.519991023770441</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.6914376309754049</v>
+        <v>0.6075329449323585</v>
       </c>
       <c r="F1981" t="n">
         <v>-0.6313417769723266</v>
@@ -47137,10 +47137,10 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.410987944419823</v>
+        <v>-5.620749659527439</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.6552951163036838</v>
+        <v>0.5713904302606374</v>
       </c>
       <c r="F1982" t="n">
         <v>-0.7201673456993321</v>
@@ -47160,10 +47160,10 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.366785107333922</v>
+        <v>-5.576546822441538</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.6788558536658811</v>
+        <v>0.5949511676228347</v>
       </c>
       <c r="F1983" t="n">
         <v>-0.6759645086134316</v>
@@ -47183,10 +47183,10 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.403764134997365</v>
+        <v>-5.613525850104981</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.6624742430697514</v>
+        <v>0.5785695570267051</v>
       </c>
       <c r="F1984" t="n">
         <v>-0.6389906068221011</v>
@@ -47206,10 +47206,10 @@
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.423822213862206</v>
+        <v>-5.633583928969822</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.7056987767068548</v>
+        <v>0.6217940906638084</v>
       </c>
       <c r="F1985" t="n">
         <v>-0.6389906068221011</v>
@@ -47229,10 +47229,10 @@
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-5.383891540684315</v>
+        <v>-5.593653255791931</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.7201117505722641</v>
+        <v>0.6362070645292177</v>
       </c>
       <c r="F1986" t="n">
         <v>-0.5990599336442107</v>
@@ -47252,10 +47252,10 @@
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-5.34342119312161</v>
+        <v>-5.553182908229227</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.7312481178356163</v>
+        <v>0.6473434317925699</v>
       </c>
       <c r="F1987" t="n">
         <v>-0.5585895860815058</v>
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.738918947566699</v>
+        <v>3.464364853866614</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-5.207695458748025</v>
+        <v>-5.487958727102021</v>
       </c>
       <c r="E1988" t="n">
-        <v>0.8027258156777553</v>
+        <v>0.6906205083361567</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.4228638517079198</v>
+        <v>-0.4933654049543001</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.632442112465961</v>
+        <v>2.590141180518133</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240608.xlsx
+++ b/tame_output/ON/bt/strategyON_20240608.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>60.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>69.3%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.8%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>50.3%</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-4.6%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-81.5%</t>
+          <t>-81.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.5%</t>
+          <t>108.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>128.2%</t>
+          <t>128.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>86.7%</t>
+          <t>87.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-52.4%</t>
+          <t>-52.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-78.5%</t>
+          <t>-77.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.9%</t>
+          <t>90.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>449.2%</t>
+          <t>453.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.1%</t>
+          <t>-10.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-710.4%</t>
+          <t>-692.6%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-1.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,27 +1150,27 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-42.0%</t>
+          <t>-42.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-28.8%</t>
+          <t>-30.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-307.2%</t>
+          <t>-300.0%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-25.5%</t>
+          <t>-25.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>33.2%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.059597089338201</v>
+        <v>-7.091245542652281</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2864306923661046</v>
+        <v>0.2737713110404725</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.624412880725885</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.475988963625198</v>
+        <v>-7.507637416939279</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1178679932601829</v>
+        <v>0.1052086119345508</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.624412880725885</v>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.792600906165847</v>
+        <v>-7.824249359479927</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.001481906912602859</v>
+        <v>-0.0111774744130293</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.624412880725885</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094113</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.138475728150656</v>
+        <v>-8.170124181464736</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1407684567356258</v>
+        <v>-0.1534278380612579</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.624412880725885</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199282</v>
+        <v>3.405960511199281</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.30205560633504</v>
+        <v>-8.33370405964912</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2077954879543786</v>
+        <v>-0.2204548692800108</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.624412880725885</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.42463335496959</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.598716948145238</v>
+        <v>-8.630365401459319</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3226810487492497</v>
+        <v>-0.3353404300748819</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.693156016459764</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923084</v>
+        <v>3.419979433923083</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.803748128919555</v>
+        <v>-8.835396582233635</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.4087198255933795</v>
+        <v>-0.4213792069190117</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.693156016459764</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297747</v>
+        <v>3.458100091297746</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.186749517662186</v>
+        <v>-9.218397970976266</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5620224824120159</v>
+        <v>-0.5746818637376481</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.693156016459764</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.36861930864722</v>
+        <v>-9.400267761961301</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.6321988828345995</v>
+        <v>-0.6448582641602316</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.875025807444799</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737167</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.728149631151222</v>
+        <v>-9.759798084465302</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7706607085381503</v>
+        <v>-0.783320089863782</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.875025807444799</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.50317028234131</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.778498694605444</v>
+        <v>-9.810147147919524</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7828843139626613</v>
+        <v>-0.7955436952882935</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.925374870899021</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539461</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.87611797202684</v>
+        <v>-9.90776642534092</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.8188902743094508</v>
+        <v>-0.831549655635083</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.022994148320417</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937497</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.02364406003248</v>
+        <v>-10.05529251334656</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8750071531901358</v>
+        <v>-0.8876665345157684</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.170520236326061</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.5027903991417</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.22790223536235</v>
+        <v>-10.25955068867643</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.9511972262034387</v>
+        <v>-0.9638566075290713</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.29815918094005</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.36971200956913</v>
+        <v>-10.40136046288321</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.003438581401718</v>
+        <v>-1.01609796272735</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.469437978585626</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440633</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.29624217790169</v>
+        <v>-10.32789063121577</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.9586789472413173</v>
+        <v>-0.9713383285669499</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.395968146918177</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.47136659528823</v>
+        <v>-10.50301504860231</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.014173493448418</v>
+        <v>-1.02683287477405</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.571092564304721</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587859441027</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.70581868930272</v>
+        <v>-10.7374671426168</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.11517349595581</v>
+        <v>-1.127832877281442</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.571092564304721</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764395</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.99362253383996</v>
+        <v>-11.02527098715404</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.236967224544682</v>
+        <v>-1.249626605870314</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.858896408841959</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390584</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.04640868944028</v>
+        <v>-11.07805714275436</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.256965896946256</v>
+        <v>-1.269625278271888</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.954571895424356</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.17244548280857</v>
+        <v>-11.20409393612265</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.304686885664457</v>
+        <v>-1.317346266990089</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.929320272614614</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.12042996883976</v>
+        <v>-11.15207842215384</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.279890344390531</v>
+        <v>-1.292549725716163</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.929320272614614</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.26210181056388</v>
+        <v>-11.29375026387796</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.338034307978921</v>
+        <v>-1.350693689304553</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.929320272614614</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940718</v>
+        <v>3.69157173394072</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.21251096613905</v>
+        <v>-11.24415941945313</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.303144560044114</v>
+        <v>-1.315803941369747</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.87972942818978</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.676841549770581</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.19970357313427</v>
+        <v>-11.23135202644835</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.311072736488888</v>
+        <v>-1.32373211781452</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.928585203198681</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615284</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.97385842041486</v>
+        <v>-11.00550687372894</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.211155602364915</v>
+        <v>-1.223814983690546</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.886658527611517</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.684843823812104</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.84927976407727</v>
+        <v>-10.88092821739135</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.160184995273819</v>
+        <v>-1.172844376599451</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.886658527611517</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646218</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.90217505212155</v>
+        <v>-10.93382350543563</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.178709336329426</v>
+        <v>-1.191368717655058</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.881703181523071</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611568</v>
+        <v>3.76895167461157</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.83004187683367</v>
+        <v>-10.86169033014775</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.144122361975637</v>
+        <v>-1.156781743301269</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.881703181523071</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.75867548422403</v>
+        <v>-10.79032393753811</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.125313067325643</v>
+        <v>-1.137972448651276</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.810336788913423</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74770266023241</v>
+        <v>3.747702660232412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.49483861701996</v>
+        <v>-10.52648707033404</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.029661801756923</v>
+        <v>-1.042321183082555</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.810336788913423</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436226</v>
+        <v>3.766317079436228</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.22759681615156</v>
+        <v>-10.25924526946564</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.9245996419089377</v>
+        <v>-0.9372590232345694</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.810336788913423</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311946</v>
+        <v>3.784684521311948</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.12968977747507</v>
+        <v>-10.16133823078915</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8857371414118025</v>
+        <v>-0.8983965227374342</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.742351039052866</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097241</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.10573623649911</v>
+        <v>-10.13738468981319</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8754872188759255</v>
+        <v>-0.8881466002015572</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.718397498076909</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78931111201777</v>
+        <v>3.789311112017771</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.841676298176314</v>
+        <v>-9.873324751490394</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7831235597085588</v>
+        <v>-0.795782941034191</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.454337559754113</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839723</v>
+        <v>3.833252747839725</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.134596674671476</v>
+        <v>-9.166245127985556</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.5030787439669249</v>
+        <v>-0.5157381252925566</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.454337559754113</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388726</v>
+        <v>3.839374447388728</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.094412376305286</v>
+        <v>-9.126060829619366</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.4866614007326073</v>
+        <v>-0.499320782058239</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.414153261387922</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.856161751626474</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.014342580767481</v>
+        <v>-9.045991034081561</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.4552666612967284</v>
+        <v>-0.4679260426223606</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.334083465850118</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291809</v>
+        <v>3.787330429291813</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.780861358537884</v>
+        <v>-8.812509811851964</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.3539497435670369</v>
+        <v>-0.3666091248926691</v>
       </c>
       <c r="F1903" t="n">
         <v>-2.100602243620519</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785786</v>
+        <v>3.80163712278579</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.631194967530369</v>
+        <v>-8.66284342084445</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.2969753974769906</v>
+        <v>-0.3096347788026224</v>
       </c>
       <c r="F1904" t="n">
         <v>-2.007698752377983</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390426</v>
+        <v>3.76318224839043</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.498919493899482</v>
+        <v>-8.530567947213562</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.2486977212776087</v>
+        <v>-0.2613571026032404</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.875423278747097</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105951</v>
+        <v>3.784718794105954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.308319819226329</v>
+        <v>-8.339968272540409</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.1696427907207103</v>
+        <v>-0.1823021720463425</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.684823604073944</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960985</v>
+        <v>3.753882571960989</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.059320020542748</v>
+        <v>-8.090968473856828</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.05713653002361907</v>
+        <v>-0.06979591134925123</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.684823604073944</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607647</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.164910010315852</v>
+        <v>-8.196558463629932</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2273484555320797</v>
+        <v>-0.2400078368577119</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.790413593847048</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987905</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.183644912434449</v>
+        <v>-8.215293365748529</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1862980745024321</v>
+        <v>-0.1989574558280642</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.79600960350718</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033368671081</v>
+        <v>3.760333686710814</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.03570487102685</v>
+        <v>-8.06735332434093</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.2470009806275599</v>
+        <v>-0.2596603619531921</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.775688687598622</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409208</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.018546720895555</v>
+        <v>-8.050195174209636</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.2488517068285203</v>
+        <v>-0.2615110881541525</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.758530537467328</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.729969716098112</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.974998314124865</v>
+        <v>-8.006646767438944</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.2383929562153373</v>
+        <v>-0.2510523375409695</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.758530537467328</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493419</v>
+        <v>3.782922533493423</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.732849920671007</v>
+        <v>-7.764498373985086</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1270712444526509</v>
+        <v>-0.1397306257782831</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.758530537467328</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722816</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.624590783548485</v>
+        <v>-7.656239236862564</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.08923546914444724</v>
+        <v>-0.1018948504700794</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.758530537467328</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792049</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.501299648731354</v>
+        <v>-7.532948102045434</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.04242092120701813</v>
+        <v>-0.05508030253265028</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.635239402650197</v>
@@ -45613,16 +45613,16 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.81245367891991</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.480150449827911</v>
+        <v>-7.51179890314199</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.02626026340831578</v>
+        <v>-0.03891964473394793</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.614090203746754</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318092</v>
+        <v>3.748328408318096</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.236385007844467</v>
+        <v>-7.268033461158546</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.06702662173211271</v>
+        <v>0.05436724040648055</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.614090203746754</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057529</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.134622187567172</v>
+        <v>-7.166270640881251</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1098560637630466</v>
+        <v>0.09719668243741442</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.600871135354325</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279185</v>
+        <v>3.826354974279188</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.884771793618097</v>
+        <v>-6.916420246932176</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2025382963263787</v>
+        <v>0.1898789150007465</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.600871135354325</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011498</v>
+        <v>3.835957987011501</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.708879701150664</v>
+        <v>-6.740528154464744</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2764942568340008</v>
+        <v>0.2638348755083686</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.600871135354325</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.780933911392991</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.537433238128201</v>
+        <v>-6.56908169144228</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.3584003480975397</v>
+        <v>0.3457409667719076</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.429424672331862</v>
@@ -45751,16 +45751,16 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.773765222632785</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.312400238459378</v>
+        <v>-6.344048691773457</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4474340255813658</v>
+        <v>0.4347746442557336</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.204391672663039</v>
@@ -45774,16 +45774,16 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883077</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.248764496225443</v>
+        <v>-6.280412949539523</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4775831235292567</v>
+        <v>0.464923742203625</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.140755930429105</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074782</v>
+        <v>3.798814771074785</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.205002314919602</v>
+        <v>-6.236650768233681</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4762822548353891</v>
+        <v>0.4636228735097569</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.140755930429105</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242296</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.964571818114742</v>
+        <v>-5.996220271428821</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5741975301822109</v>
+        <v>0.5615381488565787</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.9003254336242443</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367684</v>
+        <v>3.821593509367687</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.892329249943547</v>
+        <v>-5.923977703257626</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6070238712855089</v>
+        <v>0.5943644899598768</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.9003254336242443</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879966</v>
+        <v>3.822326997879967</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.839330927662159</v>
+        <v>-5.870979380976238</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6289017841154041</v>
+        <v>0.6162424027897719</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.8449891746223055</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502339</v>
+        <v>3.848616626502341</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.730526042182432</v>
+        <v>-5.762174495496511</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.6694218095272881</v>
+        <v>0.656762428201656</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.8449891746223055</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675939</v>
+        <v>3.81866895167594</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.510505244145421</v>
+        <v>-5.542153697459501</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.7590091657527065</v>
+        <v>0.7463497844270743</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.7037693295543253</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327452753995</v>
+        <v>3.843274527539952</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.377637555082144</v>
+        <v>-5.409286008396223</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.8280504241798408</v>
+        <v>0.815391042854209</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.7037693295543253</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496262</v>
+        <v>3.845047386496264</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.218122451562774</v>
+        <v>-5.249770904876853</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.8930023100278905</v>
+        <v>0.8803429287022588</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.5442542260349553</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551577001</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-5.073450306463037</v>
+        <v>-5.105098759777116</v>
       </c>
       <c r="E1932" t="n">
-        <v>0.9609592706292256</v>
+        <v>0.9482998893035934</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.3995820809352179</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942106</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-5.133325133820729</v>
+        <v>-5.164973587134808</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9230468310875746</v>
+        <v>0.9103874497619424</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.45945690829291</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674518</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-5.04652563604172</v>
+        <v>-5.078174089355799</v>
       </c>
       <c r="E1934" t="n">
-        <v>0.9801671235217442</v>
+        <v>0.967507742196112</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.45945690829291</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430694</v>
+        <v>3.729146398430697</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-5.048995342503526</v>
+        <v>-5.080643795817605</v>
       </c>
       <c r="E1935" t="n">
-        <v>0.9792516423104338</v>
+        <v>0.9665922609848021</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.4619266147547162</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003602</v>
+        <v>3.743220196003605</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-5.117365528827536</v>
+        <v>-5.149013982141615</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.9629104902555321</v>
+        <v>0.9502511089298999</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.4526509157185012</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.71417913950837</v>
+        <v>3.714179139508373</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.22590370974367</v>
+        <v>-5.257552163057749</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9099319265209695</v>
+        <v>0.8972725451953374</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.4526509157185012</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417703</v>
+        <v>3.710906731417706</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.256896869072375</v>
+        <v>-5.288545322386454</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.7222442278298744</v>
+        <v>0.7095848465042423</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.4526509157185012</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.746042526205901</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-5.291184324387523</v>
+        <v>-5.113071062593986</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.7130964776956032</v>
+        <v>0.7843417824130174</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.4526509157185012</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225445</v>
+        <v>3.765024323225447</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-5.402120577028771</v>
+        <v>-5.224007315235235</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.6444640054003106</v>
+        <v>0.7157093101177252</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.4526509157185012</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111297</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.605147154572005</v>
+        <v>-5.427033892778468</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.566384759602923</v>
+        <v>0.6376300643203372</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.6556774932617346</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264163</v>
+        <v>3.784343952264166</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-5.447221555636712</v>
+        <v>-5.269108293843175</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.6397273856091723</v>
+        <v>0.7109726903265869</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.6556774932617346</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742302</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-5.360978092610334</v>
+        <v>-5.182864830816797</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.6691710413935841</v>
+        <v>0.7404163461109983</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.6556774932617346</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316047</v>
+        <v>3.75202749931605</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-5.406284912009314</v>
+        <v>-5.228171650215777</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.6428240890785175</v>
+        <v>0.7140693937959317</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.6964876562709654</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803194</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-5.435318016711615</v>
+        <v>-5.257204754918078</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.6317627202306988</v>
+        <v>0.703008024948113</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.6964876562709654</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809498</v>
+        <v>3.733390600809501</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-5.342507535260755</v>
+        <v>-5.164394273467218</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.598159604702408</v>
+        <v>0.6694049094198227</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.6036771748201061</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560428</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-5.386897004590183</v>
+        <v>-5.208783742796646</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.5822772928952378</v>
+        <v>0.6535225976126524</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.6480666441495337</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472738</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-5.274225786353933</v>
+        <v>-5.096112524560396</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.6224214887014612</v>
+        <v>0.6936667934188754</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.5353954259132836</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.74304760379854</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-5.16184878517126</v>
+        <v>-4.983735523377723</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.6728635850051976</v>
+        <v>0.7441088897226118</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.5353954259132836</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498867</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-5.36008335405799</v>
+        <v>-5.181970092264454</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.6050669592190441</v>
+        <v>0.6763122639364587</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.7336299948000142</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705325</v>
+        <v>3.643069621705328</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-5.443084635083269</v>
+        <v>-5.264971373289733</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.4102221668095858</v>
+        <v>0.4814674715270004</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.7522008793271879</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.68271631072927</v>
+        <v>3.682716310729273</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-5.5516987135266</v>
+        <v>-5.373585451733064</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.486926196151459</v>
+        <v>0.5581715008688732</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.7522008793271879</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190769</v>
+        <v>3.733012441190771</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.638297296507703</v>
+        <v>-5.460184034714167</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.4667997890613407</v>
+        <v>0.5380450937787553</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.7522008793271879</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913427</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.599913633949552</v>
+        <v>-5.421800372156016</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.4795726954269699</v>
+        <v>0.5508180001443845</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.7138172167690368</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532485</v>
+        <v>3.751147197532487</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-5.422797303914386</v>
+        <v>-5.244684042120849</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.5471482562863383</v>
+        <v>0.6183935610037525</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.7138172167690368</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-5.467889548747932</v>
+        <v>-5.289776286954395</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.5297947501148332</v>
+        <v>0.6010400548322474</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.7757132599384265</v>
@@ -46562,10 +46562,10 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-5.288514127509164</v>
+        <v>-5.110400865715627</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.5953318939167547</v>
+        <v>0.6665771986341689</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.6189365017677079</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982231</v>
+        <v>3.716991718982232</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-5.333528341029771</v>
+        <v>-5.155415079236234</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.5581336638401018</v>
+        <v>0.629378968557516</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.6492853970823125</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509538</v>
+        <v>3.737026608509539</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.600532851302206</v>
+        <v>-5.422419589508669</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.4570234220700735</v>
+        <v>0.5282687267874877</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.8436484351252611</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.702309454760814</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.701730632739379</v>
+        <v>-5.523617370945842</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.4157482313917056</v>
+        <v>0.4869935361091202</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.9120572486705802</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815459</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.669255046568606</v>
+        <v>-5.49114178477507</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.4263384274143314</v>
+        <v>0.4975837321317456</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.9120572486705802</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.709510443378104</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.650216918861309</v>
+        <v>-5.472103657067772</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.4304783977054951</v>
+        <v>0.5017237024229098</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.9702408600017748</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131252</v>
+        <v>3.731064473131254</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.681343550011928</v>
+        <v>-5.503230288218391</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.5956096141839282</v>
+        <v>0.6668549189013429</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.9702408600017748</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067868</v>
+        <v>3.72244736206787</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.733663930612719</v>
+        <v>-5.555550668819182</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.5755147909297453</v>
+        <v>0.6467600956471595</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.9352939999929026</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789125</v>
+        <v>3.787425580789127</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.753921229141677</v>
+        <v>-5.57580796734814</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.5734204019150879</v>
+        <v>0.6446657066325026</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.9352939999929026</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.78150125051991</v>
+        <v>3.781501250519912</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.606178258906675</v>
+        <v>-5.428064997113138</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.711670237801111</v>
+        <v>0.7829155425185252</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.7674866427580195</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181172</v>
+        <v>3.802245929181174</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.708192941437896</v>
+        <v>-5.530079679644359</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.6736579863201033</v>
+        <v>0.744903291037518</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.7674866427580195</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.805608985394733</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.571583597343803</v>
+        <v>-5.393470335550266</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.7289640723493989</v>
+        <v>0.8002093770668131</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.6308772986639271</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890615</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.714348930166453</v>
+        <v>-5.536235668372917</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.6709384159604492</v>
+        <v>0.7421837206778634</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.7736426314865774</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.86736263679843</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.652050931390331</v>
+        <v>-5.473937669596794</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.7621931692677189</v>
+        <v>0.833438473985133</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.7736426314865774</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992192</v>
+        <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-5.450260733725173</v>
+        <v>-5.272147471931636</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.5514901207231802</v>
+        <v>0.6227354254405943</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.575624439317423</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852424</v>
+        <v>3.841444817852427</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-5.39037005208258</v>
+        <v>-5.212256790289043</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.6457366257023924</v>
+        <v>0.7169819304198071</v>
       </c>
       <c r="F1972" t="n">
         <v>-0.5157337576748295</v>
@@ -46924,16 +46924,16 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319548</v>
+        <v>3.819063300319549</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.488110596707554</v>
+        <v>-5.309997334914017</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.6212681439684467</v>
+        <v>0.6925134486858608</v>
       </c>
       <c r="F1973" t="n">
         <v>-0.5316230358078098</v>
@@ -46947,16 +46947,16 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489385</v>
+        <v>3.831819032489387</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.664448356830484</v>
+        <v>-5.486335095036947</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.5492690207439463</v>
+        <v>0.620514325461361</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.7079607959307392</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397796</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.66375898466926</v>
+        <v>-5.485645722875724</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.5480363876483643</v>
+        <v>0.6192816923657785</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.7079607959307392</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024963</v>
+        <v>3.836023391024964</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.670329949723853</v>
+        <v>-5.492216687930316</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.5452708690619632</v>
+        <v>0.6165161737793778</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.7145317609853321</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863225</v>
+        <v>3.821591150863227</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.662375979429081</v>
+        <v>-5.484262717635544</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.5484524571798723</v>
+        <v>0.6196977618972865</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.7145317609853321</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947585</v>
+        <v>3.833040181947586</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.652002603095994</v>
+        <v>-5.473889341302457</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.5589835647409118</v>
+        <v>0.630228869458326</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.7041583846522448</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326877</v>
+        <v>3.822707244326879</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-5.524318293301698</v>
+        <v>-5.346205031508161</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.614949662033355</v>
+        <v>0.6861949667507692</v>
       </c>
       <c r="F1979" t="n">
         <v>-0.5764740748579483</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314553</v>
+        <v>3.828837911314555</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.584984883704086</v>
+        <v>-5.406871621910549</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.5774376983482719</v>
+        <v>0.648683003065686</v>
       </c>
       <c r="F1980" t="n">
         <v>-0.658172391576482</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690028</v>
+        <v>3.81686606769003</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-5.519991023770441</v>
+        <v>-5.341877761976904</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.6075329449323585</v>
+        <v>0.6787782496497727</v>
       </c>
       <c r="F1981" t="n">
         <v>-0.6313417769723266</v>
@@ -47131,16 +47131,16 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674311</v>
+        <v>3.817961388674313</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.620749659527439</v>
+        <v>-5.442636397733902</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.5713904302606374</v>
+        <v>0.6426357349780516</v>
       </c>
       <c r="F1982" t="n">
         <v>-0.7201673456993321</v>
@@ -47154,16 +47154,16 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.82671377916322</v>
+        <v>3.826713779163222</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.576546822441538</v>
+        <v>-5.398433560648002</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.5949511676228347</v>
+        <v>0.6661964723402489</v>
       </c>
       <c r="F1983" t="n">
         <v>-0.6759645086134316</v>
@@ -47177,16 +47177,16 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022905</v>
+        <v>3.838228663022907</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.613525850104981</v>
+        <v>-5.435412588311444</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.5785695570267051</v>
+        <v>0.6498148617441193</v>
       </c>
       <c r="F1984" t="n">
         <v>-0.6389906068221011</v>
@@ -47200,16 +47200,16 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042139</v>
+        <v>3.863924114042141</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.633583928969822</v>
+        <v>-5.455470667176285</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.6217940906638084</v>
+        <v>0.6930393953812231</v>
       </c>
       <c r="F1985" t="n">
         <v>-0.6389906068221011</v>
@@ -47223,16 +47223,16 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86536771507828</v>
+        <v>3.865367715078282</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-5.593653255791931</v>
+        <v>-5.415539993998395</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.6362070645292177</v>
+        <v>0.7074523692466324</v>
       </c>
       <c r="F1986" t="n">
         <v>-0.5990599336442107</v>
@@ -47246,16 +47246,16 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232396</v>
+        <v>3.864518876232398</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-5.553182908229227</v>
+        <v>-5.37506964643569</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.6473434317925699</v>
+        <v>0.7185887365099841</v>
       </c>
       <c r="F1987" t="n">
         <v>-0.5585895860815058</v>
@@ -47269,16 +47269,16 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.464364853866614</v>
+        <v>3.783458091208544</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-5.487958727102021</v>
+        <v>-5.309845465308484</v>
       </c>
       <c r="E1988" t="n">
-        <v>0.6906205083361567</v>
+        <v>0.7618658130535714</v>
       </c>
       <c r="F1988" t="n">
         <v>-0.4933654049543001</v>

--- a/tame_output/ON/bt/strategyON_20240608.xlsx
+++ b/tame_output/ON/bt/strategyON_20240608.xlsx
@@ -615,11 +615,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-06-07</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>50.1%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-06-07</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.6%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-23.0%</t>
+          <t>-30.4%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-81.0%</t>
+          <t>-81.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.9%</t>
+          <t>108.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-06-07</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>128.6%</t>
+          <t>128.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>87.3%</t>
+          <t>87.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.5%</t>
+          <t>-78.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>90.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.2%</t>
+          <t>453.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.4%</t>
+          <t>-10.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-692.6%</t>
+          <t>-705.8%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-1.9%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,16 +1084,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-06-07</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-42.1%</t>
+          <t>-42.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-30.0%</t>
+          <t>-30.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-300.0%</t>
+          <t>-305.3%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-31.0%</t>
+          <t>-30.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,17 +1260,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-06-07</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>70.1%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-25.0%</t>
+          <t>-24.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-273.3%</t>
+          <t>-266.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-06-07</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-17.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-187.0%</t>
+          <t>-165.5%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1988"/>
+  <dimension ref="A1:G1989"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44440,16 +44440,16 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191733</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.091245542652281</v>
+        <v>-7.084582814975136</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2737713110404725</v>
+        <v>0.2764364021113304</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.624412880725885</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.507637416939279</v>
+        <v>-7.500974689262134</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1052086119345508</v>
+        <v>0.1078737030054087</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.624412880725885</v>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.824249359479927</v>
+        <v>-7.817586631802782</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.0111774744130293</v>
+        <v>-0.008512383342171415</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.624412880725885</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094113</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.170124181464736</v>
+        <v>-8.16346145378759</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1534278380612579</v>
+        <v>-0.1507627469903996</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.624412880725885</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.405960511199282</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.33370405964912</v>
+        <v>-8.327041331971975</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2204548692800108</v>
+        <v>-0.2177897782091525</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.624412880725885</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.42463335496959</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.630365401459319</v>
+        <v>-8.623702673782173</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3353404300748819</v>
+        <v>-0.3326753390040236</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.693156016459764</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923083</v>
+        <v>3.419979433923084</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.835396582233635</v>
+        <v>-8.828733854556489</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.4213792069190117</v>
+        <v>-0.4187141158481533</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.693156016459764</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297746</v>
+        <v>3.458100091297747</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.218397970976266</v>
+        <v>-9.21173524329912</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5746818637376481</v>
+        <v>-0.5720167726667897</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.693156016459764</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317613</v>
+        <v>3.447750501317614</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.400267761961301</v>
+        <v>-9.393605034284155</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.6448582641602316</v>
+        <v>-0.6421931730893733</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.875025807444799</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.759798084465302</v>
+        <v>-9.753135356788157</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.783320089863782</v>
+        <v>-0.7806549987929241</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.875025807444799</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.50317028234131</v>
+        <v>3.503170282341311</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.810147147919524</v>
+        <v>-9.803484420242379</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7955436952882935</v>
+        <v>-0.7928786042174352</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.925374870899021</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539461</v>
+        <v>3.501052558539462</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.90776642534092</v>
+        <v>-9.901103697663775</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.831549655635083</v>
+        <v>-0.8288845645642247</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.022994148320417</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.05529251334656</v>
+        <v>-10.04862978566942</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8876665345157684</v>
+        <v>-0.8850014434449096</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.170520236326061</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.25955068867643</v>
+        <v>-10.25288796099928</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.9638566075290713</v>
+        <v>-0.9611915164582125</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.29815918094005</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.496851904729892</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.40136046288321</v>
+        <v>-10.39469773520607</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.01609796272735</v>
+        <v>-1.013432871656492</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.469437978585626</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440635</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.32789063121577</v>
+        <v>-10.32122790353862</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.9713383285669499</v>
+        <v>-0.9686732374960911</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.395968146918177</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.490059241608602</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.50301504860231</v>
+        <v>-10.49635232092516</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.02683287477405</v>
+        <v>-1.024167783703192</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.571092564304721</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410273</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.7374671426168</v>
+        <v>-10.73080441493965</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.127832877281442</v>
+        <v>-1.125167786210584</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.571092564304721</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764398</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.02527098715404</v>
+        <v>-11.01860825947689</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.249626605870314</v>
+        <v>-1.246961514799456</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.858896408841959</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390587</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.07805714275436</v>
+        <v>-11.07139441507722</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.269625278271888</v>
+        <v>-1.26696018720103</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.954571895424356</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297399</v>
+        <v>3.4921016412974</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.20409393612265</v>
+        <v>-11.19743120844551</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.317346266990089</v>
+        <v>-1.314681175919231</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.929320272614614</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322544</v>
+        <v>3.573674025322545</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.15207842215384</v>
+        <v>-11.14541569447669</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.292549725716163</v>
+        <v>-1.289884634645305</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.929320272614614</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158922</v>
+        <v>3.600038265158923</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.29375026387796</v>
+        <v>-11.28708753620081</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.350693689304553</v>
+        <v>-1.348028598233695</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.929320272614614</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.69157173394072</v>
+        <v>3.691571733940721</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.24415941945313</v>
+        <v>-11.23749669177598</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.315803941369747</v>
+        <v>-1.313138850298888</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.87972942818978</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770581</v>
+        <v>3.676841549770582</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.23135202644835</v>
+        <v>-11.22468929877121</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.32373211781452</v>
+        <v>-1.321067026743662</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.928585203198681</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615284</v>
+        <v>3.685161381615285</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.00550687372894</v>
+        <v>-10.99884414605179</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.223814983690546</v>
+        <v>-1.221149892619688</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.886658527611517</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812104</v>
+        <v>3.684843823812105</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.88092821739135</v>
+        <v>-10.8742654897142</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.172844376599451</v>
+        <v>-1.170179285528592</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.886658527611517</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646218</v>
+        <v>3.710935533646219</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.93382350543563</v>
+        <v>-10.92716077775849</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.191368717655058</v>
+        <v>-1.1887036265842</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.881703181523071</v>
@@ -45090,10 +45090,10 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.86169033014775</v>
+        <v>-10.85502760247061</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.156781743301269</v>
+        <v>-1.154116652230411</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.881703181523071</v>
@@ -45113,10 +45113,10 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.79032393753811</v>
+        <v>-10.78366120986096</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.137972448651276</v>
+        <v>-1.135307357580417</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.810336788913423</v>
@@ -45136,10 +45136,10 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.52648707033404</v>
+        <v>-10.51982434265689</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.042321183082555</v>
+        <v>-1.039656092011696</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.810336788913423</v>
@@ -45159,10 +45159,10 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.25924526946564</v>
+        <v>-10.25258254178849</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.9372590232345694</v>
+        <v>-0.9345939321637116</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.810336788913423</v>
@@ -45182,10 +45182,10 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.16133823078915</v>
+        <v>-10.154675503112</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8983965227374342</v>
+        <v>-0.8957314316665763</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.742351039052866</v>
@@ -45205,10 +45205,10 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.13738468981319</v>
+        <v>-10.13072196213604</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8881466002015572</v>
+        <v>-0.8854815091306993</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.718397498076909</v>
@@ -45228,10 +45228,10 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.873324751490394</v>
+        <v>-9.866662023813248</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.795782941034191</v>
+        <v>-0.7931178499633327</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.454337559754113</v>
@@ -45251,10 +45251,10 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.166245127985556</v>
+        <v>-9.159582400308411</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.5157381252925566</v>
+        <v>-0.5130730342216987</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.454337559754113</v>
@@ -45274,10 +45274,10 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.126060829619366</v>
+        <v>-9.11939810194222</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.499320782058239</v>
+        <v>-0.4966556909873812</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.414153261387922</v>
@@ -45297,10 +45297,10 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.045991034081561</v>
+        <v>-9.039328306404416</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.4679260426223606</v>
+        <v>-0.4652609515515023</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.334083465850118</v>
@@ -45320,10 +45320,10 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.812509811851964</v>
+        <v>-8.805847084174818</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.3666091248926691</v>
+        <v>-0.3639440338218107</v>
       </c>
       <c r="F1903" t="n">
         <v>-2.100602243620519</v>
@@ -45343,10 +45343,10 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.66284342084445</v>
+        <v>-8.656180693167304</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.3096347788026224</v>
+        <v>-0.3069696877317645</v>
       </c>
       <c r="F1904" t="n">
         <v>-2.007698752377983</v>
@@ -45366,10 +45366,10 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.530567947213562</v>
+        <v>-8.523905219536417</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.2613571026032404</v>
+        <v>-0.2586920115323825</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.875423278747097</v>
@@ -45389,10 +45389,10 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.339968272540409</v>
+        <v>-8.333305544863263</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.1823021720463425</v>
+        <v>-0.1796370809754841</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.684823604073944</v>
@@ -45412,10 +45412,10 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.090968473856828</v>
+        <v>-8.084305746179682</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.06979591134925123</v>
+        <v>-0.0671308202783929</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.684823604073944</v>
@@ -45435,10 +45435,10 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.196558463629932</v>
+        <v>-8.189895735952787</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2400078368577119</v>
+        <v>-0.2373427457868535</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.790413593847048</v>
@@ -45458,10 +45458,10 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.215293365748529</v>
+        <v>-8.208630638071384</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1989574558280642</v>
+        <v>-0.1962923647572059</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.79600960350718</v>
@@ -45481,10 +45481,10 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.06735332434093</v>
+        <v>-8.060690596663784</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.2596603619531921</v>
+        <v>-0.2569952708823338</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.775688687598622</v>
@@ -45504,10 +45504,10 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.050195174209636</v>
+        <v>-8.04353244653249</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.2615110881541525</v>
+        <v>-0.2588459970832941</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.758530537467328</v>
@@ -45527,10 +45527,10 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.006646767438944</v>
+        <v>-7.9999840397618</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.2510523375409695</v>
+        <v>-0.2483872464701111</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.758530537467328</v>
@@ -45550,10 +45550,10 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.764498373985086</v>
+        <v>-7.757835646307941</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1397306257782831</v>
+        <v>-0.1370655347074248</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.758530537467328</v>
@@ -45573,10 +45573,10 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.656239236862564</v>
+        <v>-7.64957650918542</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.1018948504700794</v>
+        <v>-0.09922975939922107</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.758530537467328</v>
@@ -45596,10 +45596,10 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.532948102045434</v>
+        <v>-7.526285374368289</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.05508030253265028</v>
+        <v>-0.05241521146179196</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.635239402650197</v>
@@ -45619,10 +45619,10 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.51179890314199</v>
+        <v>-7.505136175464846</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.03891964473394793</v>
+        <v>-0.03625455366308961</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.614090203746754</v>
@@ -45642,10 +45642,10 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.268033461158546</v>
+        <v>-7.261370733481401</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.05436724040648055</v>
+        <v>0.05703233147733888</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.614090203746754</v>
@@ -45665,10 +45665,10 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.166270640881251</v>
+        <v>-7.159607913204106</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.09719668243741442</v>
+        <v>0.09986177350827274</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.600871135354325</v>
@@ -45688,10 +45688,10 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.916420246932176</v>
+        <v>-6.909757519255032</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.1898789150007465</v>
+        <v>0.1925440060716048</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.600871135354325</v>
@@ -45711,10 +45711,10 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.740528154464744</v>
+        <v>-6.733865426787599</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2638348755083686</v>
+        <v>0.2664999665792269</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.600871135354325</v>
@@ -45734,10 +45734,10 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.56908169144228</v>
+        <v>-6.562418963765135</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.3457409667719076</v>
+        <v>0.3484060578427659</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.429424672331862</v>
@@ -45757,10 +45757,10 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.344048691773457</v>
+        <v>-6.337385964096312</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4347746442557336</v>
+        <v>0.437439735326592</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.204391672663039</v>
@@ -45780,10 +45780,10 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.280412949539523</v>
+        <v>-6.273750221862378</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.464923742203625</v>
+        <v>0.4675888332744829</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.140755930429105</v>
@@ -45803,10 +45803,10 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.236650768233681</v>
+        <v>-6.229988040556536</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4636228735097569</v>
+        <v>0.4662879645806153</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.140755930429105</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242296</v>
+        <v>3.797694884242295</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.996220271428821</v>
+        <v>-5.989557543751676</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5615381488565787</v>
+        <v>0.564203239927437</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.9003254336242443</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367687</v>
+        <v>3.821593509367686</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.923977703257626</v>
+        <v>-5.917314975580481</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.5943644899598768</v>
+        <v>0.5970295810307351</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.9003254336242443</v>
@@ -45872,10 +45872,10 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.870979380976238</v>
+        <v>-5.864316653299094</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6162424027897719</v>
+        <v>0.6189074938606303</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.8449891746223055</v>
@@ -45895,10 +45895,10 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.762174495496511</v>
+        <v>-5.755511767819367</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.656762428201656</v>
+        <v>0.6594275192725143</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.8449891746223055</v>
@@ -45918,10 +45918,10 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.542153697459501</v>
+        <v>-5.535490969782356</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.7463497844270743</v>
+        <v>0.7490148754979327</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.7037693295543253</v>
@@ -45941,10 +45941,10 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.409286008396223</v>
+        <v>-5.402623280719078</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.815391042854209</v>
+        <v>0.8180561339250669</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.7037693295543253</v>
@@ -45964,10 +45964,10 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.249770904876853</v>
+        <v>-5.243108177199709</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.8803429287022588</v>
+        <v>0.8830080197731167</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.5442542260349553</v>
@@ -45987,10 +45987,10 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-5.105098759777116</v>
+        <v>-5.098436032099971</v>
       </c>
       <c r="E1932" t="n">
-        <v>0.9482998893035934</v>
+        <v>0.9509649803744518</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.3995820809352179</v>
@@ -46010,10 +46010,10 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-5.164973587134808</v>
+        <v>-5.158310859457663</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9103874497619424</v>
+        <v>0.9130525408328007</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.45945690829291</v>
@@ -46033,10 +46033,10 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-5.078174089355799</v>
+        <v>-5.071511361678654</v>
       </c>
       <c r="E1934" t="n">
-        <v>0.967507742196112</v>
+        <v>0.9701728332669703</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.45945690829291</v>
@@ -46056,10 +46056,10 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-5.080643795817605</v>
+        <v>-5.07398106814046</v>
       </c>
       <c r="E1935" t="n">
-        <v>0.9665922609848021</v>
+        <v>0.96925735205566</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.4619266147547162</v>
@@ -46079,10 +46079,10 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-5.149013982141615</v>
+        <v>-5.142351254464471</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.9502511089298999</v>
+        <v>0.9529162000007583</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.4526509157185012</v>
@@ -46102,10 +46102,10 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.257552163057749</v>
+        <v>-5.250889435380604</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.8972725451953374</v>
+        <v>0.8999376362661957</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.4526509157185012</v>
@@ -46125,10 +46125,10 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.288545322386454</v>
+        <v>-5.28188259470931</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.7095848465042423</v>
+        <v>0.7122499375751006</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.4526509157185012</v>
@@ -46148,10 +46148,10 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-5.113071062593986</v>
+        <v>-5.317647419955884</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.7843417824130174</v>
+        <v>0.7025112394682584</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.4526509157185012</v>
@@ -46171,10 +46171,10 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-5.224007315235235</v>
+        <v>-5.428583672597133</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.7157093101177252</v>
+        <v>0.6338787671729658</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.4526509157185012</v>
@@ -46194,10 +46194,10 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.427033892778468</v>
+        <v>-5.631610250140366</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.6376300643203372</v>
+        <v>0.5557995213755782</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.6556774932617346</v>
@@ -46217,10 +46217,10 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-5.269108293843175</v>
+        <v>-5.473684651205073</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.7109726903265869</v>
+        <v>0.6291421473818279</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.6556774932617346</v>
@@ -46240,10 +46240,10 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-5.182864830816797</v>
+        <v>-5.387441188178696</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.7404163461109983</v>
+        <v>0.6585858031662393</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.6556774932617346</v>
@@ -46263,10 +46263,10 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-5.228171650215777</v>
+        <v>-5.432748007577676</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.7140693937959317</v>
+        <v>0.6322388508511727</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.6964876562709654</v>
@@ -46286,10 +46286,10 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-5.257204754918078</v>
+        <v>-5.461781112279977</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.703008024948113</v>
+        <v>0.621177482003354</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.6964876562709654</v>
@@ -46309,10 +46309,10 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-5.164394273467218</v>
+        <v>-5.368970630829117</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.6694049094198227</v>
+        <v>0.5875743664750632</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.6036771748201061</v>
@@ -46332,10 +46332,10 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-5.208783742796646</v>
+        <v>-5.413360100158545</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.6535225976126524</v>
+        <v>0.5716920546678934</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.6480666441495337</v>
@@ -46355,10 +46355,10 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-5.096112524560396</v>
+        <v>-5.300688881922294</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.6936667934188754</v>
+        <v>0.6118362504741164</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.5353954259132836</v>
@@ -46378,10 +46378,10 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.983735523377723</v>
+        <v>-5.188311880739621</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.7441088897226118</v>
+        <v>0.6622783467778528</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.5353954259132836</v>
@@ -46401,10 +46401,10 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-5.181970092264454</v>
+        <v>-5.386546449626352</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.6763122639364587</v>
+        <v>0.5944817209916993</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.7336299948000142</v>
@@ -46424,10 +46424,10 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-5.264971373289733</v>
+        <v>-5.469547730651631</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.4814674715270004</v>
+        <v>0.399636928582241</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.7522008793271879</v>
@@ -46447,10 +46447,10 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-5.373585451733064</v>
+        <v>-5.578161809094962</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.5581715008688732</v>
+        <v>0.4763409579241142</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.7522008793271879</v>
@@ -46470,10 +46470,10 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.460184034714167</v>
+        <v>-5.664760392076065</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.5380450937787553</v>
+        <v>0.4562145508339963</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.7522008793271879</v>
@@ -46493,10 +46493,10 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.421800372156016</v>
+        <v>-5.626376729517914</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.5508180001443845</v>
+        <v>0.4689874571996251</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.7138172167690368</v>
@@ -46516,10 +46516,10 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-5.244684042120849</v>
+        <v>-5.449260399482748</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.6183935610037525</v>
+        <v>0.5365630180589935</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.7138172167690368</v>
@@ -46539,10 +46539,10 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-5.289776286954395</v>
+        <v>-5.494352644316294</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.6010400548322474</v>
+        <v>0.5192095118874884</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.7757132599384265</v>
@@ -46562,10 +46562,10 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-5.110400865715627</v>
+        <v>-5.314977223077526</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.6665771986341689</v>
+        <v>0.5847466556894099</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.6189365017677079</v>
@@ -46585,10 +46585,10 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-5.155415079236234</v>
+        <v>-5.359991436598133</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.629378968557516</v>
+        <v>0.547548425612757</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.6492853970823125</v>
@@ -46608,10 +46608,10 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.422419589508669</v>
+        <v>-5.626995946870568</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.5282687267874877</v>
+        <v>0.4464381838427287</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.8436484351252611</v>
@@ -46631,10 +46631,10 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.523617370945842</v>
+        <v>-5.72819372830774</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.4869935361091202</v>
+        <v>0.4051629931643612</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.9120572486705802</v>
@@ -46654,10 +46654,10 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.49114178477507</v>
+        <v>-5.695718142136968</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.4975837321317456</v>
+        <v>0.4157531891869866</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.9120572486705802</v>
@@ -46677,10 +46677,10 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.472103657067772</v>
+        <v>-5.676680014429671</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.5017237024229098</v>
+        <v>0.4198931594781503</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.9702408600017748</v>
@@ -46700,10 +46700,10 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.503230288218391</v>
+        <v>-5.707806645580289</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.6668549189013429</v>
+        <v>0.5850243759565839</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.9702408600017748</v>
@@ -46723,10 +46723,10 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.555550668819182</v>
+        <v>-5.760127026181081</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.6467600956471595</v>
+        <v>0.5649295527024005</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.9352939999929026</v>
@@ -46746,10 +46746,10 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.57580796734814</v>
+        <v>-5.780384324710039</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.6446657066325026</v>
+        <v>0.5628351636877431</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.9352939999929026</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519912</v>
+        <v>3.781501250519911</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.428064997113138</v>
+        <v>-5.632641354475036</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.7829155425185252</v>
+        <v>0.7010849995737662</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.7674866427580195</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181174</v>
+        <v>3.802245929181173</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.530079679644359</v>
+        <v>-5.734656037006258</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.744903291037518</v>
+        <v>0.6630727480927585</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.7674866427580195</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394733</v>
+        <v>3.805608985394732</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.393470335550266</v>
+        <v>-5.598046692912165</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8002093770668131</v>
+        <v>0.7183788341220541</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.6308772986639271</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890615</v>
+        <v>3.798239794890614</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.536235668372917</v>
+        <v>-5.740812025734815</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.7421837206778634</v>
+        <v>0.6603531777331044</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.7736426314865774</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.86736263679843</v>
+        <v>3.867362636798429</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.473937669596794</v>
+        <v>-5.678514026958693</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.833438473985133</v>
+        <v>0.751607931040374</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.7736426314865774</v>
@@ -46884,10 +46884,10 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-5.272147471931636</v>
+        <v>-5.476723829293535</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.6227354254405943</v>
+        <v>0.5409048824958353</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.575624439317423</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852427</v>
+        <v>3.841444817852426</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-5.212256790289043</v>
+        <v>-5.416833147650942</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.7169819304198071</v>
+        <v>0.6351513874750481</v>
       </c>
       <c r="F1972" t="n">
         <v>-0.5157337576748295</v>
@@ -46930,10 +46930,10 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.309997334914017</v>
+        <v>-5.514573692275916</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.6925134486858608</v>
+        <v>0.6106829057411018</v>
       </c>
       <c r="F1973" t="n">
         <v>-0.5316230358078098</v>
@@ -46953,10 +46953,10 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.486335095036947</v>
+        <v>-5.690911452398845</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.620514325461361</v>
+        <v>0.5386837825166015</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.7079607959307392</v>
@@ -46976,10 +46976,10 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.485645722875724</v>
+        <v>-5.690222080237622</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.6192816923657785</v>
+        <v>0.5374511494210195</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.7079607959307392</v>
@@ -46999,10 +46999,10 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.492216687930316</v>
+        <v>-5.696793045292215</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.6165161737793778</v>
+        <v>0.5346856308346188</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.7145317609853321</v>
@@ -47022,10 +47022,10 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.484262717635544</v>
+        <v>-5.688839074997443</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.6196977618972865</v>
+        <v>0.5378672189525275</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.7145317609853321</v>
@@ -47045,10 +47045,10 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.473889341302457</v>
+        <v>-5.678465698664356</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.630228869458326</v>
+        <v>0.548398326513567</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.7041583846522448</v>
@@ -47068,10 +47068,10 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-5.346205031508161</v>
+        <v>-5.550781388870059</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.6861949667507692</v>
+        <v>0.6043644238060102</v>
       </c>
       <c r="F1979" t="n">
         <v>-0.5764740748579483</v>
@@ -47091,10 +47091,10 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.406871621910549</v>
+        <v>-5.611447979272448</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.648683003065686</v>
+        <v>0.566852460120927</v>
       </c>
       <c r="F1980" t="n">
         <v>-0.658172391576482</v>
@@ -47114,10 +47114,10 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-5.341877761976904</v>
+        <v>-5.546454119338803</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.6787782496497727</v>
+        <v>0.5969477067050137</v>
       </c>
       <c r="F1981" t="n">
         <v>-0.6313417769723266</v>
@@ -47137,10 +47137,10 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.442636397733902</v>
+        <v>-5.647212755095801</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.6426357349780516</v>
+        <v>0.5608051920332926</v>
       </c>
       <c r="F1982" t="n">
         <v>-0.7201673456993321</v>
@@ -47160,10 +47160,10 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.398433560648002</v>
+        <v>-5.6030099180099</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.6661964723402489</v>
+        <v>0.5843659293954899</v>
       </c>
       <c r="F1983" t="n">
         <v>-0.6759645086134316</v>
@@ -47183,10 +47183,10 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.435412588311444</v>
+        <v>-5.639988945673343</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.6498148617441193</v>
+        <v>0.5679843187993603</v>
       </c>
       <c r="F1984" t="n">
         <v>-0.6389906068221011</v>
@@ -47206,10 +47206,10 @@
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.455470667176285</v>
+        <v>-5.660047024538184</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.6930393953812231</v>
+        <v>0.6112088524364636</v>
       </c>
       <c r="F1985" t="n">
         <v>-0.6389906068221011</v>
@@ -47229,10 +47229,10 @@
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-5.415539993998395</v>
+        <v>-5.620116351360293</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.7074523692466324</v>
+        <v>0.6256218263018729</v>
       </c>
       <c r="F1986" t="n">
         <v>-0.5990599336442107</v>
@@ -47252,10 +47252,10 @@
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-5.37506964643569</v>
+        <v>-5.579646003797588</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.7185887365099841</v>
+        <v>0.6367581935652251</v>
       </c>
       <c r="F1987" t="n">
         <v>-0.5585895860815058</v>
@@ -47269,22 +47269,45 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.783458091208544</v>
+        <v>3.842576394162115</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-5.309845465308484</v>
+        <v>-5.442411396884313</v>
       </c>
       <c r="E1988" t="n">
-        <v>0.7618658130535714</v>
+        <v>0.7088394404232403</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.4933654049543001</v>
+        <v>-0.4213549791682301</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.590141180518133</v>
+        <v>2.633347435989775</v>
+      </c>
+    </row>
+    <row r="1989">
+      <c r="A1989" s="2" t="n">
+        <v>45451</v>
+      </c>
+      <c r="B1989" t="n">
+        <v>3.782131786488419</v>
+      </c>
+      <c r="C1989" t="n">
+        <v>2.812547058895741</v>
+      </c>
+      <c r="D1989" t="n">
+        <v>-5.442411396884313</v>
+      </c>
+      <c r="E1989" t="n">
+        <v>0.7088394404232403</v>
+      </c>
+      <c r="F1989" t="n">
+        <v>-0.4213549791682301</v>
+      </c>
+      <c r="G1989" t="n">
+        <v>2.805610855882108</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240608.xlsx
+++ b/tame_output/ON/bt/strategyON_20240608.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-81.4%</t>
+          <t>-81.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.7%</t>
+          <t>108.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>128.4%</t>
+          <t>128.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>87.0%</t>
+          <t>87.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-78.0%</t>
+          <t>-77.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.1%</t>
+          <t>90.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.3%</t>
+          <t>453.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.1%</t>
+          <t>-10.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-705.8%</t>
+          <t>-692.6%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-1.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-42.0%</t>
+          <t>-42.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-30.5%</t>
+          <t>-30.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-305.3%</t>
+          <t>-300.0%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-30.2%</t>
+          <t>-31.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-24.2%</t>
+          <t>-25.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-266.1%</t>
+          <t>-273.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -44440,16 +44440,16 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191733</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.084582814975136</v>
+        <v>-7.091245542652281</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2764364021113304</v>
+        <v>0.2737713110404725</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.624412880725885</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.500974689262134</v>
+        <v>-7.507637416939279</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1078737030054087</v>
+        <v>0.1052086119345508</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.624412880725885</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.817586631802782</v>
+        <v>-7.824249359479927</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.008512383342171415</v>
+        <v>-0.0111774744130293</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.624412880725885</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.16346145378759</v>
+        <v>-8.170124181464736</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1507627469903996</v>
+        <v>-0.1534278380612579</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.624412880725885</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.327041331971975</v>
+        <v>-8.33370405964912</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2177897782091525</v>
+        <v>-0.2204548692800108</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.624412880725885</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.623702673782173</v>
+        <v>-8.630365401459319</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3326753390040236</v>
+        <v>-0.3353404300748819</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.693156016459764</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.828733854556489</v>
+        <v>-8.835396582233635</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.4187141158481533</v>
+        <v>-0.4213792069190117</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.693156016459764</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.21173524329912</v>
+        <v>-9.218397970976266</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5720167726667897</v>
+        <v>-0.5746818637376481</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.693156016459764</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317614</v>
+        <v>3.447750501317613</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.393605034284155</v>
+        <v>-9.400267761961301</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.6421931730893733</v>
+        <v>-0.6448582641602316</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.875025807444799</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737167</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.753135356788157</v>
+        <v>-9.759798084465302</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7806549987929241</v>
+        <v>-0.783320089863782</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.875025807444799</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341311</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.803484420242379</v>
+        <v>-9.810147147919524</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7928786042174352</v>
+        <v>-0.7955436952882935</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.925374870899021</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539462</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.901103697663775</v>
+        <v>-9.90776642534092</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.8288845645642247</v>
+        <v>-0.831549655635083</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.022994148320417</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.04862978566942</v>
+        <v>-10.05529251334656</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8850014434449096</v>
+        <v>-0.8876665345157684</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.170520236326061</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.5027903991417</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.25288796099928</v>
+        <v>-10.25955068867643</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.9611915164582125</v>
+        <v>-0.9638566075290713</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.29815918094005</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729892</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.39469773520607</v>
+        <v>-10.40136046288321</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.013432871656492</v>
+        <v>-1.01609796272735</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.469437978585626</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440635</v>
+        <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.32122790353862</v>
+        <v>-10.32789063121577</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.9686732374960911</v>
+        <v>-0.9713383285669499</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.395968146918177</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608602</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.49635232092516</v>
+        <v>-10.50301504860231</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.024167783703192</v>
+        <v>-1.02683287477405</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.571092564304721</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410273</v>
+        <v>3.48587859441027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.73080441493965</v>
+        <v>-10.7374671426168</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.125167786210584</v>
+        <v>-1.127832877281442</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.571092564304721</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764398</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.01860825947689</v>
+        <v>-11.02527098715404</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.246961514799456</v>
+        <v>-1.249626605870314</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.858896408841959</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390587</v>
+        <v>3.493716014390584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.07139441507722</v>
+        <v>-11.07805714275436</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.26696018720103</v>
+        <v>-1.269625278271888</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.954571895424356</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.4921016412974</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.19743120844551</v>
+        <v>-11.20409393612265</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.314681175919231</v>
+        <v>-1.317346266990089</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.929320272614614</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322545</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.14541569447669</v>
+        <v>-11.15207842215384</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.289884634645305</v>
+        <v>-1.292549725716163</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.929320272614614</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158923</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.28708753620081</v>
+        <v>-11.29375026387796</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.348028598233695</v>
+        <v>-1.350693689304553</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.929320272614614</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940721</v>
+        <v>3.691571733940718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.23749669177598</v>
+        <v>-11.24415941945313</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.313138850298888</v>
+        <v>-1.315803941369747</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.87972942818978</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770582</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.22468929877121</v>
+        <v>-11.23135202644835</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.321067026743662</v>
+        <v>-1.32373211781452</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.928585203198681</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615285</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.99884414605179</v>
+        <v>-11.00550687372894</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.221149892619688</v>
+        <v>-1.223814983690546</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.886658527611517</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812105</v>
+        <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.8742654897142</v>
+        <v>-10.88092821739135</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.170179285528592</v>
+        <v>-1.172844376599451</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.886658527611517</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646219</v>
+        <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.92716077775849</v>
+        <v>-10.93382350543563</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.1887036265842</v>
+        <v>-1.191368717655058</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.881703181523071</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.76895167461157</v>
+        <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.85502760247061</v>
+        <v>-10.86169033014775</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.154116652230411</v>
+        <v>-1.156781743301269</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.881703181523071</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955328</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.78366120986096</v>
+        <v>-10.79032393753811</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.135307357580417</v>
+        <v>-1.137972448651276</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.810336788913423</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232412</v>
+        <v>3.74770266023241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.51982434265689</v>
+        <v>-10.52648707033404</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.039656092011696</v>
+        <v>-1.042321183082555</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.810336788913423</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436228</v>
+        <v>3.766317079436226</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.25258254178849</v>
+        <v>-10.25924526946564</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.9345939321637116</v>
+        <v>-0.9372590232345694</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.810336788913423</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311948</v>
+        <v>3.784684521311946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.154675503112</v>
+        <v>-10.16133823078915</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8957314316665763</v>
+        <v>-0.8983965227374342</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.742351039052866</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.13072196213604</v>
+        <v>-10.13738468981319</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8854815091306993</v>
+        <v>-0.8881466002015572</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.718397498076909</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017771</v>
+        <v>3.78931111201777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.866662023813248</v>
+        <v>-9.873324751490394</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7931178499633327</v>
+        <v>-0.795782941034191</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.454337559754113</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839725</v>
+        <v>3.833252747839723</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.159582400308411</v>
+        <v>-9.166245127985556</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.5130730342216987</v>
+        <v>-0.5157381252925566</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.454337559754113</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388728</v>
+        <v>3.839374447388726</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.11939810194222</v>
+        <v>-9.126060829619366</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.4966556909873812</v>
+        <v>-0.499320782058239</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.414153261387922</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626474</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.039328306404416</v>
+        <v>-9.045991034081561</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.4652609515515023</v>
+        <v>-0.4679260426223606</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.334083465850118</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291813</v>
+        <v>3.787330429291809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.805847084174818</v>
+        <v>-8.812509811851964</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.3639440338218107</v>
+        <v>-0.3666091248926691</v>
       </c>
       <c r="F1903" t="n">
         <v>-2.100602243620519</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.80163712278579</v>
+        <v>3.801637122785786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.656180693167304</v>
+        <v>-8.66284342084445</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.3069696877317645</v>
+        <v>-0.3096347788026224</v>
       </c>
       <c r="F1904" t="n">
         <v>-2.007698752377983</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.76318224839043</v>
+        <v>3.763182248390426</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.523905219536417</v>
+        <v>-8.530567947213562</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.2586920115323825</v>
+        <v>-0.2613571026032404</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.875423278747097</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105954</v>
+        <v>3.784718794105951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.333305544863263</v>
+        <v>-8.339968272540409</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.1796370809754841</v>
+        <v>-0.1823021720463425</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.684823604073944</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960989</v>
+        <v>3.753882571960985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.084305746179682</v>
+        <v>-8.090968473856828</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.0671308202783929</v>
+        <v>-0.06979591134925123</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.684823604073944</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607647</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.189895735952787</v>
+        <v>-8.196558463629932</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2373427457868535</v>
+        <v>-0.2400078368577119</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.790413593847048</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987905</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.208630638071384</v>
+        <v>-8.215293365748529</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1962923647572059</v>
+        <v>-0.1989574558280642</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.79600960350718</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710814</v>
+        <v>3.76033368671081</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.060690596663784</v>
+        <v>-8.06735332434093</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.2569952708823338</v>
+        <v>-0.2596603619531921</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.775688687598622</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409208</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.04353244653249</v>
+        <v>-8.050195174209636</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.2588459970832941</v>
+        <v>-0.2615110881541525</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.758530537467328</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098112</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.9999840397618</v>
+        <v>-8.006646767438944</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.2483872464701111</v>
+        <v>-0.2510523375409695</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.758530537467328</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493423</v>
+        <v>3.782922533493419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.757835646307941</v>
+        <v>-7.764498373985086</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1370655347074248</v>
+        <v>-0.1397306257782831</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.758530537467328</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.828551486722816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.64957650918542</v>
+        <v>-7.656239236862564</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.09922975939922107</v>
+        <v>-0.1018948504700794</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.758530537467328</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792049</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.526285374368289</v>
+        <v>-7.532948102045434</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.05241521146179196</v>
+        <v>-0.05508030253265028</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.635239402650197</v>
@@ -45613,16 +45613,16 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.81245367891991</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.505136175464846</v>
+        <v>-7.51179890314199</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.03625455366308961</v>
+        <v>-0.03891964473394793</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.614090203746754</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318096</v>
+        <v>3.748328408318092</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.261370733481401</v>
+        <v>-7.268033461158546</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.05703233147733888</v>
+        <v>0.05436724040648055</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.614090203746754</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057529</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.159607913204106</v>
+        <v>-7.166270640881251</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.09986177350827274</v>
+        <v>0.09719668243741442</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.600871135354325</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279188</v>
+        <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.909757519255032</v>
+        <v>-6.916420246932176</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.1925440060716048</v>
+        <v>0.1898789150007465</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.600871135354325</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011501</v>
+        <v>3.835957987011498</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.733865426787599</v>
+        <v>-6.740528154464744</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2664999665792269</v>
+        <v>0.2638348755083686</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.600871135354325</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392991</v>
+        <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.562418963765135</v>
+        <v>-6.56908169144228</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.3484060578427659</v>
+        <v>0.3457409667719076</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.429424672331862</v>
@@ -45751,16 +45751,16 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632785</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.337385964096312</v>
+        <v>-6.344048691773457</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.437439735326592</v>
+        <v>0.4347746442557336</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.204391672663039</v>
@@ -45774,16 +45774,16 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883077</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.273750221862378</v>
+        <v>-6.280412949539523</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4675888332744829</v>
+        <v>0.464923742203625</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.140755930429105</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074785</v>
+        <v>3.798814771074782</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.229988040556536</v>
+        <v>-6.236650768233681</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4662879645806153</v>
+        <v>0.4636228735097569</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.140755930429105</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242295</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.989557543751676</v>
+        <v>-5.996220271428821</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.564203239927437</v>
+        <v>0.5615381488565787</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.9003254336242443</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367686</v>
+        <v>3.821593509367684</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.917314975580481</v>
+        <v>-5.923977703257626</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.5970295810307351</v>
+        <v>0.5943644899598768</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.9003254336242443</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879967</v>
+        <v>3.822326997879966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.864316653299094</v>
+        <v>-5.870979380976238</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6189074938606303</v>
+        <v>0.6162424027897719</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.8449891746223055</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502341</v>
+        <v>3.848616626502339</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.755511767819367</v>
+        <v>-5.762174495496511</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.6594275192725143</v>
+        <v>0.656762428201656</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.8449891746223055</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.81866895167594</v>
+        <v>3.818668951675939</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.535490969782356</v>
+        <v>-5.542153697459501</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.7490148754979327</v>
+        <v>0.7463497844270743</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.7037693295543253</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539952</v>
+        <v>3.84327452753995</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.402623280719078</v>
+        <v>-5.409286008396223</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.8180561339250669</v>
+        <v>0.815391042854209</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.7037693295543253</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496264</v>
+        <v>3.845047386496262</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.243108177199709</v>
+        <v>-5.249770904876853</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.8830080197731167</v>
+        <v>0.8803429287022588</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.5442542260349553</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577001</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-5.098436032099971</v>
+        <v>-5.105098759777116</v>
       </c>
       <c r="E1932" t="n">
-        <v>0.9509649803744518</v>
+        <v>0.9482998893035934</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.3995820809352179</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942106</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-5.158310859457663</v>
+        <v>-5.164973587134808</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9130525408328007</v>
+        <v>0.9103874497619424</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.45945690829291</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674518</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-5.071511361678654</v>
+        <v>-5.078174089355799</v>
       </c>
       <c r="E1934" t="n">
-        <v>0.9701728332669703</v>
+        <v>0.967507742196112</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.45945690829291</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430697</v>
+        <v>3.729146398430694</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-5.07398106814046</v>
+        <v>-5.080643795817605</v>
       </c>
       <c r="E1935" t="n">
-        <v>0.96925735205566</v>
+        <v>0.9665922609848021</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.4619266147547162</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003605</v>
+        <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-5.142351254464471</v>
+        <v>-5.149013982141615</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.9529162000007583</v>
+        <v>0.9502511089298999</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.4526509157185012</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508373</v>
+        <v>3.71417913950837</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.250889435380604</v>
+        <v>-5.257552163057749</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.8999376362661957</v>
+        <v>0.8972725451953374</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.4526509157185012</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417706</v>
+        <v>3.710906731417703</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.28188259470931</v>
+        <v>-5.288545322386454</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.7122499375751006</v>
+        <v>0.7095848465042423</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.4526509157185012</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205901</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-5.317647419955884</v>
+        <v>-5.113071062593986</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.7025112394682584</v>
+        <v>0.7843417824130174</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.4526509157185012</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225447</v>
+        <v>3.765024323225445</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-5.428583672597133</v>
+        <v>-5.224007315235235</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.6338787671729658</v>
+        <v>0.7157093101177252</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.4526509157185012</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111297</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.631610250140366</v>
+        <v>-5.427033892778468</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.5557995213755782</v>
+        <v>0.6376300643203372</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.6556774932617346</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264166</v>
+        <v>3.784343952264163</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-5.473684651205073</v>
+        <v>-5.269108293843175</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.6291421473818279</v>
+        <v>0.7109726903265869</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.6556774932617346</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742302</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-5.387441188178696</v>
+        <v>-5.182864830816797</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.6585858031662393</v>
+        <v>0.7404163461109983</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.6556774932617346</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.75202749931605</v>
+        <v>3.752027499316047</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-5.432748007577676</v>
+        <v>-5.228171650215777</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.6322388508511727</v>
+        <v>0.7140693937959317</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.6964876562709654</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803194</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-5.461781112279977</v>
+        <v>-5.257204754918078</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.621177482003354</v>
+        <v>0.703008024948113</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.6964876562709654</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809501</v>
+        <v>3.733390600809498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-5.368970630829117</v>
+        <v>-5.164394273467218</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.5875743664750632</v>
+        <v>0.6694049094198227</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.6036771748201061</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560428</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-5.413360100158545</v>
+        <v>-5.208783742796646</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.5716920546678934</v>
+        <v>0.6535225976126524</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.6480666441495337</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-5.300688881922294</v>
+        <v>-5.096112524560396</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.6118362504741164</v>
+        <v>0.6936667934188754</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.5353954259132836</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.74304760379854</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-5.188311880739621</v>
+        <v>-4.983735523377723</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.6622783467778528</v>
+        <v>0.7441088897226118</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.5353954259132836</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498867</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-5.386546449626352</v>
+        <v>-5.181970092264454</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.5944817209916993</v>
+        <v>0.6763122639364587</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.7336299948000142</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705328</v>
+        <v>3.643069621705325</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-5.469547730651631</v>
+        <v>-5.264971373289733</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.399636928582241</v>
+        <v>0.4814674715270004</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.7522008793271879</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729273</v>
+        <v>3.68271631072927</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-5.578161809094962</v>
+        <v>-5.373585451733064</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.4763409579241142</v>
+        <v>0.5581715008688732</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.7522008793271879</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190771</v>
+        <v>3.733012441190769</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.664760392076065</v>
+        <v>-5.460184034714167</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.4562145508339963</v>
+        <v>0.5380450937787553</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.7522008793271879</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913427</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.626376729517914</v>
+        <v>-5.421800372156016</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.4689874571996251</v>
+        <v>0.5508180001443845</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.7138172167690368</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532487</v>
+        <v>3.751147197532485</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-5.449260399482748</v>
+        <v>-5.244684042120849</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.5365630180589935</v>
+        <v>0.6183935610037525</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.7138172167690368</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-5.494352644316294</v>
+        <v>-5.289776286954395</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.5192095118874884</v>
+        <v>0.6010400548322474</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.7757132599384265</v>
@@ -46562,10 +46562,10 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-5.314977223077526</v>
+        <v>-5.110400865715627</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.5847466556894099</v>
+        <v>0.6665771986341689</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.6189365017677079</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982232</v>
+        <v>3.716991718982231</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-5.359991436598133</v>
+        <v>-5.155415079236234</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.547548425612757</v>
+        <v>0.629378968557516</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.6492853970823125</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509539</v>
+        <v>3.737026608509538</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.626995946870568</v>
+        <v>-5.422419589508669</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.4464381838427287</v>
+        <v>0.5282687267874877</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.8436484351252611</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760814</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.72819372830774</v>
+        <v>-5.523617370945842</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.4051629931643612</v>
+        <v>0.4869935361091202</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.9120572486705802</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815459</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.695718142136968</v>
+        <v>-5.49114178477507</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.4157531891869866</v>
+        <v>0.4975837321317456</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.9120572486705802</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378104</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.676680014429671</v>
+        <v>-5.472103657067772</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.4198931594781503</v>
+        <v>0.5017237024229098</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.9702408600017748</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131254</v>
+        <v>3.731064473131252</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.707806645580289</v>
+        <v>-5.503230288218391</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.5850243759565839</v>
+        <v>0.6668549189013429</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.9702408600017748</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.72244736206787</v>
+        <v>3.722447362067868</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.760127026181081</v>
+        <v>-5.555550668819182</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.5649295527024005</v>
+        <v>0.6467600956471595</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.9352939999929026</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789127</v>
+        <v>3.787425580789125</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.780384324710039</v>
+        <v>-5.57580796734814</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.5628351636877431</v>
+        <v>0.6446657066325026</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.9352939999929026</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519911</v>
+        <v>3.78150125051991</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.632641354475036</v>
+        <v>-5.428064997113138</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.7010849995737662</v>
+        <v>0.7829155425185252</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.7674866427580195</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181173</v>
+        <v>3.802245929181172</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.734656037006258</v>
+        <v>-5.530079679644359</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.6630727480927585</v>
+        <v>0.744903291037518</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.7674866427580195</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394732</v>
+        <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.598046692912165</v>
+        <v>-5.393470335550266</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.7183788341220541</v>
+        <v>0.8002093770668131</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.6308772986639271</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890614</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.740812025734815</v>
+        <v>-5.536235668372917</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.6603531777331044</v>
+        <v>0.7421837206778634</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.7736426314865774</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798429</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.678514026958693</v>
+        <v>-5.473937669596794</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.751607931040374</v>
+        <v>0.833438473985133</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.7736426314865774</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992193</v>
+        <v>3.848729139992192</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-5.476723829293535</v>
+        <v>-5.272147471931636</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.5409048824958353</v>
+        <v>0.6227354254405943</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.575624439317423</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852426</v>
+        <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-5.416833147650942</v>
+        <v>-5.212256790289043</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.6351513874750481</v>
+        <v>0.7169819304198071</v>
       </c>
       <c r="F1972" t="n">
         <v>-0.5157337576748295</v>
@@ -46924,16 +46924,16 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319549</v>
+        <v>3.819063300319548</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.514573692275916</v>
+        <v>-5.309997334914017</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.6106829057411018</v>
+        <v>0.6925134486858608</v>
       </c>
       <c r="F1973" t="n">
         <v>-0.5316230358078098</v>
@@ -46947,16 +46947,16 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489387</v>
+        <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.690911452398845</v>
+        <v>-5.486335095036947</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.5386837825166015</v>
+        <v>0.620514325461361</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.7079607959307392</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397796</v>
+        <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.690222080237622</v>
+        <v>-5.485645722875724</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.5374511494210195</v>
+        <v>0.6192816923657785</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.7079607959307392</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024964</v>
+        <v>3.836023391024963</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.696793045292215</v>
+        <v>-5.492216687930316</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.5346856308346188</v>
+        <v>0.6165161737793778</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.7145317609853321</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863227</v>
+        <v>3.821591150863225</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.688839074997443</v>
+        <v>-5.484262717635544</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.5378672189525275</v>
+        <v>0.6196977618972865</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.7145317609853321</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947586</v>
+        <v>3.833040181947585</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.678465698664356</v>
+        <v>-5.473889341302457</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.548398326513567</v>
+        <v>0.630228869458326</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.7041583846522448</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326879</v>
+        <v>3.822707244326877</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-5.550781388870059</v>
+        <v>-5.346205031508161</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.6043644238060102</v>
+        <v>0.6861949667507692</v>
       </c>
       <c r="F1979" t="n">
         <v>-0.5764740748579483</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314555</v>
+        <v>3.828837911314553</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.611447979272448</v>
+        <v>-5.406871621910549</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.566852460120927</v>
+        <v>0.648683003065686</v>
       </c>
       <c r="F1980" t="n">
         <v>-0.658172391576482</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.81686606769003</v>
+        <v>3.816866067690028</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-5.546454119338803</v>
+        <v>-5.341877761976904</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.5969477067050137</v>
+        <v>0.6787782496497727</v>
       </c>
       <c r="F1981" t="n">
         <v>-0.6313417769723266</v>
@@ -47131,16 +47131,16 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674313</v>
+        <v>3.817961388674311</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.647212755095801</v>
+        <v>-5.442636397733902</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.5608051920332926</v>
+        <v>0.6426357349780516</v>
       </c>
       <c r="F1982" t="n">
         <v>-0.7201673456993321</v>
@@ -47154,16 +47154,16 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163222</v>
+        <v>3.82671377916322</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.6030099180099</v>
+        <v>-5.398433560648002</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.5843659293954899</v>
+        <v>0.6661964723402489</v>
       </c>
       <c r="F1983" t="n">
         <v>-0.6759645086134316</v>
@@ -47177,16 +47177,16 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022907</v>
+        <v>3.838228663022905</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.639988945673343</v>
+        <v>-5.435412588311444</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.5679843187993603</v>
+        <v>0.6498148617441193</v>
       </c>
       <c r="F1984" t="n">
         <v>-0.6389906068221011</v>
@@ -47200,16 +47200,16 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042141</v>
+        <v>3.863924114042139</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.660047024538184</v>
+        <v>-5.455470667176285</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.6112088524364636</v>
+        <v>0.6930393953812231</v>
       </c>
       <c r="F1985" t="n">
         <v>-0.6389906068221011</v>
@@ -47223,16 +47223,16 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078282</v>
+        <v>3.86536771507828</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-5.620116351360293</v>
+        <v>-5.415539993998395</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.6256218263018729</v>
+        <v>0.7074523692466324</v>
       </c>
       <c r="F1986" t="n">
         <v>-0.5990599336442107</v>
@@ -47246,16 +47246,16 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232398</v>
+        <v>3.864518876232396</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-5.579646003797588</v>
+        <v>-5.37506964643569</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.6367581935652251</v>
+        <v>0.7185887365099841</v>
       </c>
       <c r="F1987" t="n">
         <v>-0.5585895860815058</v>
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162115</v>
+        <v>3.842576394162113</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-5.442411396884313</v>
+        <v>-5.309845465308484</v>
       </c>
       <c r="E1988" t="n">
-        <v>0.7088394404232403</v>
+        <v>0.7618658130535714</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.4213549791682301</v>
+        <v>-0.4933654049543001</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.633347435989775</v>
+        <v>2.590141180518133</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,19 +47292,19 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.782131786488419</v>
+        <v>3.782131786488418</v>
       </c>
       <c r="C1989" t="n">
         <v>2.812547058895741</v>
       </c>
       <c r="D1989" t="n">
-        <v>-5.442411396884313</v>
+        <v>-5.309845465308484</v>
       </c>
       <c r="E1989" t="n">
-        <v>0.7088394404232403</v>
+        <v>0.7618658130535714</v>
       </c>
       <c r="F1989" t="n">
-        <v>-0.4213549791682301</v>
+        <v>-0.4933654049543001</v>
       </c>
       <c r="G1989" t="n">
         <v>2.805610855882108</v>

--- a/tame_output/ON/bt/strategyON_20240608.xlsx
+++ b/tame_output/ON/bt/strategyON_20240608.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>52.4%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-30.4%</t>
+          <t>-21.7%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-81.0%</t>
+          <t>-80.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.9%</t>
+          <t>108.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>128.5%</t>
+          <t>128.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-52.5%</t>
+          <t>-52.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.6%</t>
+          <t>-77.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>90.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.2%</t>
+          <t>453.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-692.6%</t>
+          <t>-689.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-1.9%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-42.1%</t>
+          <t>-42.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-30.0%</t>
+          <t>-28.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-300.0%</t>
+          <t>-292.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-165.5%</t>
+          <t>-156.8%</t>
         </is>
       </c>
     </row>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.091245542652281</v>
+        <v>-7.059597089338201</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2737713110404725</v>
+        <v>0.2864306923661046</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.624412880725885</v>
@@ -44463,16 +44463,16 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.305023265108636</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.507637416939279</v>
+        <v>-7.475988963625198</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1052086119345508</v>
+        <v>0.1178679932601829</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.624412880725885</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.824249359479927</v>
+        <v>-7.792600906165847</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.0111774744130293</v>
+        <v>0.001481906912602859</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.624412880725885</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.170124181464736</v>
+        <v>-8.138475728150656</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1534278380612579</v>
+        <v>-0.1407684567356258</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.624412880725885</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199282</v>
+        <v>3.405960511199283</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.33370405964912</v>
+        <v>-8.30205560633504</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2204548692800108</v>
+        <v>-0.2077954879543786</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.624412880725885</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.42463335496959</v>
+        <v>3.424633354969591</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.630365401459319</v>
+        <v>-8.598716948145238</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3353404300748819</v>
+        <v>-0.3226810487492497</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.693156016459764</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923084</v>
+        <v>3.419979433923085</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.835396582233635</v>
+        <v>-8.803748128919555</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.4213792069190117</v>
+        <v>-0.4087198255933795</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.693156016459764</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297747</v>
+        <v>3.458100091297748</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.218397970976266</v>
+        <v>-9.186749517662186</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5746818637376481</v>
+        <v>-0.5620224824120159</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.693156016459764</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317613</v>
+        <v>3.447750501317614</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.400267761961301</v>
+        <v>-9.36861930864722</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.6448582641602316</v>
+        <v>-0.6321988828345995</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.875025807444799</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737167</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.759798084465302</v>
+        <v>-9.728149631151222</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.783320089863782</v>
+        <v>-0.7706607085381503</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.875025807444799</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.50317028234131</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.810147147919524</v>
+        <v>-9.778498694605444</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7955436952882935</v>
+        <v>-0.7828843139626613</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.925374870899021</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539461</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.90776642534092</v>
+        <v>-9.87611797202684</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.831549655635083</v>
+        <v>-0.8188902743094508</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.022994148320417</v>
@@ -44722,10 +44722,10 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.05529251334656</v>
+        <v>-10.02364406003248</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8876665345157684</v>
+        <v>-0.8750071531901358</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.170520236326061</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.5027903991417</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.25955068867643</v>
+        <v>-10.22790223536235</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.9638566075290713</v>
+        <v>-0.9511972262034387</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.29815918094005</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.40136046288321</v>
+        <v>-10.36971200956913</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.01609796272735</v>
+        <v>-1.003438581401718</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.469437978585626</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440633</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.32789063121577</v>
+        <v>-10.29624217790169</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.9713383285669499</v>
+        <v>-0.9586789472413173</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.395968146918177</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.50301504860231</v>
+        <v>-10.47136659528823</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.02683287477405</v>
+        <v>-1.014173493448418</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.571092564304721</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587859441027</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.7374671426168</v>
+        <v>-10.70581868930272</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.127832877281442</v>
+        <v>-1.11517349595581</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.571092564304721</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764395</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.02527098715404</v>
+        <v>-10.99362253383996</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.249626605870314</v>
+        <v>-1.236967224544682</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.858896408841959</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390584</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.07805714275436</v>
+        <v>-11.04640868944028</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.269625278271888</v>
+        <v>-1.256965896946256</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.954571895424356</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.20409393612265</v>
+        <v>-11.17244548280857</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.317346266990089</v>
+        <v>-1.304686885664457</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.929320272614614</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.15207842215384</v>
+        <v>-11.12042996883976</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.292549725716163</v>
+        <v>-1.279890344390531</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.929320272614614</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.29375026387796</v>
+        <v>-11.26210181056388</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.350693689304553</v>
+        <v>-1.338034307978921</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.929320272614614</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940718</v>
+        <v>3.691571733940719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.24415941945313</v>
+        <v>-11.21251096613905</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.315803941369747</v>
+        <v>-1.303144560044114</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.87972942818978</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.67684154977058</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.23135202644835</v>
+        <v>-11.19970357313427</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.32373211781452</v>
+        <v>-1.311072736488888</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.928585203198681</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.00550687372894</v>
+        <v>-10.97385842041486</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.223814983690546</v>
+        <v>-1.211155602364915</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.886658527611517</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.684843823812103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.88092821739135</v>
+        <v>-10.84927976407727</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.172844376599451</v>
+        <v>-1.160184995273819</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.886658527611517</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.93382350543563</v>
+        <v>-10.90217505212155</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.191368717655058</v>
+        <v>-1.178709336329426</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.881703181523071</v>
@@ -45090,10 +45090,10 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.86169033014775</v>
+        <v>-10.83004187683367</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.156781743301269</v>
+        <v>-1.144122361975637</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.881703181523071</v>
@@ -45113,10 +45113,10 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.79032393753811</v>
+        <v>-10.75867548422403</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.137972448651276</v>
+        <v>-1.125313067325643</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.810336788913423</v>
@@ -45136,10 +45136,10 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.52648707033404</v>
+        <v>-10.49483861701996</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.042321183082555</v>
+        <v>-1.029661801756923</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.810336788913423</v>
@@ -45159,10 +45159,10 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.25924526946564</v>
+        <v>-10.22759681615156</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.9372590232345694</v>
+        <v>-0.9245996419089377</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.810336788913423</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311946</v>
+        <v>3.784684521311947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.16133823078915</v>
+        <v>-10.12968977747507</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8983965227374342</v>
+        <v>-0.8857371414118025</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.742351039052866</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097241</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.13738468981319</v>
+        <v>-10.10573623649911</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8881466002015572</v>
+        <v>-0.8754872188759255</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.718397498076909</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78931111201777</v>
+        <v>3.789311112017772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.873324751490394</v>
+        <v>-9.841676298176314</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.795782941034191</v>
+        <v>-0.7831235597085588</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.454337559754113</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839723</v>
+        <v>3.833252747839725</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.166245127985556</v>
+        <v>-9.134596674671476</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.5157381252925566</v>
+        <v>-0.5030787439669249</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.454337559754113</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388726</v>
+        <v>3.839374447388728</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.126060829619366</v>
+        <v>-9.094412376305286</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.499320782058239</v>
+        <v>-0.4866614007326073</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.414153261387922</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.856161751626473</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.045991034081561</v>
+        <v>-9.014342580767481</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.4679260426223606</v>
+        <v>-0.4552666612967284</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.334083465850118</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291809</v>
+        <v>3.787330429291811</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.812509811851964</v>
+        <v>-8.780861358537884</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.3666091248926691</v>
+        <v>-0.3539497435670369</v>
       </c>
       <c r="F1903" t="n">
         <v>-2.100602243620519</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785786</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.66284342084445</v>
+        <v>-8.631194967530369</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.3096347788026224</v>
+        <v>-0.2969753974769906</v>
       </c>
       <c r="F1904" t="n">
         <v>-2.007698752377983</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390426</v>
+        <v>3.763182248390428</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.530567947213562</v>
+        <v>-8.498919493899482</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.2613571026032404</v>
+        <v>-0.2486977212776087</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.875423278747097</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105951</v>
+        <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.339968272540409</v>
+        <v>-8.308319819226329</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.1823021720463425</v>
+        <v>-0.1696427907207103</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.684823604073944</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960985</v>
+        <v>3.753882571960987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.090968473856828</v>
+        <v>-8.059320020542748</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.06979591134925123</v>
+        <v>-0.05713653002361907</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.684823604073944</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.196558463629932</v>
+        <v>-8.164910010315852</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2400078368577119</v>
+        <v>-0.2273484555320797</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.790413593847048</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.215293365748529</v>
+        <v>-8.183644912434449</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1989574558280642</v>
+        <v>-0.1862980745024321</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.79600960350718</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033368671081</v>
+        <v>3.760333686710812</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.06735332434093</v>
+        <v>-8.03570487102685</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.2596603619531921</v>
+        <v>-0.2470009806275599</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.775688687598622</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409206</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.050195174209636</v>
+        <v>-8.018546720895555</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.2615110881541525</v>
+        <v>-0.2488517068285203</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.758530537467328</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.006646767438944</v>
+        <v>-7.974998314124865</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.2510523375409695</v>
+        <v>-0.2383929562153373</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.758530537467328</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493419</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.764498373985086</v>
+        <v>-7.732849920671007</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1397306257782831</v>
+        <v>-0.1270712444526509</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.758530537467328</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722816</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.656239236862564</v>
+        <v>-7.624590783548485</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.1018948504700794</v>
+        <v>-0.08923546914444724</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.758530537467328</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.532948102045434</v>
+        <v>-7.501299648731354</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.05508030253265028</v>
+        <v>-0.04242092120701813</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.635239402650197</v>
@@ -45613,16 +45613,16 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919908</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.51179890314199</v>
+        <v>-7.480150449827911</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.03891964473394793</v>
+        <v>-0.02626026340831578</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.614090203746754</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318092</v>
+        <v>3.748328408318094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.268033461158546</v>
+        <v>-7.236385007844467</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.05436724040648055</v>
+        <v>0.06702662173211271</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.614090203746754</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.166270640881251</v>
+        <v>-7.134622187567172</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.09719668243741442</v>
+        <v>0.1098560637630466</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.600871135354325</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279185</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.916420246932176</v>
+        <v>-6.884771793618097</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.1898789150007465</v>
+        <v>0.2025382963263787</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.600871135354325</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011498</v>
+        <v>3.8359579870115</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.740528154464744</v>
+        <v>-6.708879701150664</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2638348755083686</v>
+        <v>0.2764942568340008</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.600871135354325</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.780933911392989</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.56908169144228</v>
+        <v>-6.537433238128201</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.3457409667719076</v>
+        <v>0.3584003480975397</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.429424672331862</v>
@@ -45751,16 +45751,16 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.773765222632783</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.344048691773457</v>
+        <v>-6.312400238459378</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4347746442557336</v>
+        <v>0.4474340255813658</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.204391672663039</v>
@@ -45774,16 +45774,16 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883075</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.280412949539523</v>
+        <v>-6.248764496225443</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.464923742203625</v>
+        <v>0.4775831235292567</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.140755930429105</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074782</v>
+        <v>3.798814771074784</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.236650768233681</v>
+        <v>-6.205002314919602</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4636228735097569</v>
+        <v>0.4762822548353891</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.140755930429105</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.996220271428821</v>
+        <v>-5.964571818114742</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5615381488565787</v>
+        <v>0.5741975301822109</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.9003254336242443</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367684</v>
+        <v>3.821593509367686</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.923977703257626</v>
+        <v>-5.892329249943547</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.5943644899598768</v>
+        <v>0.6070238712855089</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.9003254336242443</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879966</v>
+        <v>3.822326997879967</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.870979380976238</v>
+        <v>-5.839330927662159</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6162424027897719</v>
+        <v>0.6289017841154041</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.8449891746223055</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502339</v>
+        <v>3.84861662650234</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.762174495496511</v>
+        <v>-5.730526042182432</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.656762428201656</v>
+        <v>0.6694218095272881</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.8449891746223055</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675939</v>
+        <v>3.81866895167594</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.542153697459501</v>
+        <v>-5.510505244145421</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.7463497844270743</v>
+        <v>0.7590091657527065</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.7037693295543253</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327452753995</v>
+        <v>3.843274527539952</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.409286008396223</v>
+        <v>-5.377637555082144</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.815391042854209</v>
+        <v>0.8280504241798408</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.7037693295543253</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496262</v>
+        <v>3.845047386496264</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.249770904876853</v>
+        <v>-5.218122451562774</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.8803429287022588</v>
+        <v>0.8930023100278905</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.5442542260349553</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551577</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-5.105098759777116</v>
+        <v>-5.073450306463037</v>
       </c>
       <c r="E1932" t="n">
-        <v>0.9482998893035934</v>
+        <v>0.9609592706292256</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.3995820809352179</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-5.164973587134808</v>
+        <v>-5.133325133820729</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9103874497619424</v>
+        <v>0.9230468310875746</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.45945690829291</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674516</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-5.078174089355799</v>
+        <v>-5.04652563604172</v>
       </c>
       <c r="E1934" t="n">
-        <v>0.967507742196112</v>
+        <v>0.9801671235217442</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.45945690829291</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430694</v>
+        <v>3.729146398430696</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-5.080643795817605</v>
+        <v>-5.048995342503526</v>
       </c>
       <c r="E1935" t="n">
-        <v>0.9665922609848021</v>
+        <v>0.9792516423104338</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.4619266147547162</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003602</v>
+        <v>3.743220196003604</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-5.149013982141615</v>
+        <v>-5.117365528827536</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.9502511089298999</v>
+        <v>0.9629104902555321</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.4526509157185012</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.71417913950837</v>
+        <v>3.714179139508372</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.257552163057749</v>
+        <v>-5.22590370974367</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.8972725451953374</v>
+        <v>0.9099319265209695</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.4526509157185012</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417703</v>
+        <v>3.710906731417705</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.288545322386454</v>
+        <v>-5.256896869072375</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.7095848465042423</v>
+        <v>0.7222442278298744</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.4526509157185012</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.746042526205901</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-5.113071062593986</v>
+        <v>-5.081422609279906</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.7843417824130174</v>
+        <v>0.7970011637386496</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.4526509157185012</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225445</v>
+        <v>3.765024323225447</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-5.224007315235235</v>
+        <v>-5.192358861921155</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.7157093101177252</v>
+        <v>0.7283686914433569</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.4526509157185012</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111295</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.427033892778468</v>
+        <v>-5.395385439464389</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.6376300643203372</v>
+        <v>0.6502894456459694</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.6556774932617346</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264163</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-5.269108293843175</v>
+        <v>-5.237459840529096</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.7109726903265869</v>
+        <v>0.7236320716522191</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.6556774932617346</v>
@@ -46240,10 +46240,10 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-5.182864830816797</v>
+        <v>-5.151216377502718</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.7404163461109983</v>
+        <v>0.7530757274366304</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.6556774932617346</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316047</v>
+        <v>3.752027499316048</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-5.228171650215777</v>
+        <v>-5.196523196901698</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.7140693937959317</v>
+        <v>0.7267287751215639</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.6964876562709654</v>
@@ -46286,10 +46286,10 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-5.257204754918078</v>
+        <v>-5.225556301603999</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.703008024948113</v>
+        <v>0.7156674062737451</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.6964876562709654</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809498</v>
+        <v>3.733390600809499</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-5.164394273467218</v>
+        <v>-5.132745820153139</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.6694049094198227</v>
+        <v>0.6820642907454544</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.6036771748201061</v>
@@ -46332,10 +46332,10 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-5.208783742796646</v>
+        <v>-5.177135289482567</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.6535225976126524</v>
+        <v>0.6661819789382846</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.6480666441495337</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472738</v>
+        <v>3.721077195472739</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-5.096112524560396</v>
+        <v>-5.064464071246316</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.6936667934188754</v>
+        <v>0.7063261747445075</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.5353954259132836</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798538</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.983735523377723</v>
+        <v>-4.952087070063643</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.7441088897226118</v>
+        <v>0.756768271048244</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.5353954259132836</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498866</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-5.181970092264454</v>
+        <v>-5.150321638950374</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.6763122639364587</v>
+        <v>0.6889716452620904</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.7336299948000142</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705325</v>
+        <v>3.643069621705326</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-5.264971373289733</v>
+        <v>-5.233322919975653</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.4814674715270004</v>
+        <v>0.4941268528526321</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.7522008793271879</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.68271631072927</v>
+        <v>3.682716310729271</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-5.373585451733064</v>
+        <v>-5.341936998418984</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.5581715008688732</v>
+        <v>0.5708308821945054</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.7522008793271879</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190769</v>
+        <v>3.73301244119077</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.460184034714167</v>
+        <v>-5.428535581400087</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.5380450937787553</v>
+        <v>0.5507044751043875</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.7522008793271879</v>
@@ -46493,10 +46493,10 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.421800372156016</v>
+        <v>-5.390151918841936</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.5508180001443845</v>
+        <v>0.5634773814700162</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.7138172167690368</v>
@@ -46516,10 +46516,10 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-5.244684042120849</v>
+        <v>-5.21303558880677</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.6183935610037525</v>
+        <v>0.6310529423293847</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.7138172167690368</v>
@@ -46539,10 +46539,10 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-5.289776286954395</v>
+        <v>-5.258127833640316</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.6010400548322474</v>
+        <v>0.6136994361578796</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.7757132599384265</v>
@@ -46562,10 +46562,10 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-5.110400865715627</v>
+        <v>-5.078752412401548</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.6665771986341689</v>
+        <v>0.679236579959801</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.6189365017677079</v>
@@ -46585,10 +46585,10 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-5.155415079236234</v>
+        <v>-5.123766625922155</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.629378968557516</v>
+        <v>0.6420383498831481</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.6492853970823125</v>
@@ -46608,10 +46608,10 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.422419589508669</v>
+        <v>-5.39077113619459</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.5282687267874877</v>
+        <v>0.5409281081131199</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.8436484351252611</v>
@@ -46631,10 +46631,10 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.523617370945842</v>
+        <v>-5.491968917631763</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.4869935361091202</v>
+        <v>0.4996529174347524</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.9120572486705802</v>
@@ -46654,10 +46654,10 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.49114178477507</v>
+        <v>-5.45949333146099</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.4975837321317456</v>
+        <v>0.5102431134573777</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.9120572486705802</v>
@@ -46677,10 +46677,10 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.472103657067772</v>
+        <v>-5.440455203753693</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.5017237024229098</v>
+        <v>0.5143830837485415</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.9702408600017748</v>
@@ -46700,10 +46700,10 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.503230288218391</v>
+        <v>-5.471581834904311</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.6668549189013429</v>
+        <v>0.679514300226975</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.9702408600017748</v>
@@ -46723,10 +46723,10 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.555550668819182</v>
+        <v>-5.523902215505103</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.6467600956471595</v>
+        <v>0.6594194769727917</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.9352939999929026</v>
@@ -46746,10 +46746,10 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.57580796734814</v>
+        <v>-5.544159514034061</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.6446657066325026</v>
+        <v>0.6573250879581343</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.9352939999929026</v>
@@ -46769,10 +46769,10 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.428064997113138</v>
+        <v>-5.396416543799059</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.7829155425185252</v>
+        <v>0.7955749238441574</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.7674866427580195</v>
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181172</v>
+        <v>3.802245929181173</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.957291587209009</v>
+        <v>3.019035585656189</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.530079679644359</v>
+        <v>-5.49843122633028</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.744903291037518</v>
+        <v>0.8193066708103296</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.7674866427580195</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.496799601554198</v>
+        <v>2.558543600001378</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.957953935600667</v>
+        <v>3.019697934047847</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.393470335550266</v>
+        <v>-5.361821882236187</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8002093770668131</v>
+        <v>0.8746127568396251</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.6308772986639271</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.579427556402312</v>
+        <v>2.641171554849492</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.957034412340778</v>
+        <v>3.018778410787958</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.536235668372917</v>
+        <v>-5.504587215058837</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.7421837206778634</v>
+        <v>0.8165871004506755</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.7736426314865774</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.492848833448832</v>
+        <v>2.554592831896012</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798428</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.023369966137599</v>
+        <v>3.085113964584778</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.473937669596794</v>
+        <v>-5.442289216282715</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.833438473985133</v>
+        <v>0.9078418537579451</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.7736426314865774</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.559184387245653</v>
+        <v>2.620928385692832</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992192</v>
+        <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.731950838526997</v>
+        <v>2.793694836974177</v>
       </c>
       <c r="D1971" t="n">
-        <v>-5.272147471931636</v>
+        <v>-5.240499018617557</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.6227354254405943</v>
+        <v>0.6971388052134064</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.575624439317423</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.386576174936543</v>
+        <v>2.448320173383723</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852424</v>
+        <v>3.841444817852425</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.802241070849172</v>
+        <v>2.863985069296352</v>
       </c>
       <c r="D1972" t="n">
-        <v>-5.212256790289043</v>
+        <v>-5.180608336974964</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.7169819304198071</v>
+        <v>0.7913853101926192</v>
       </c>
       <c r="F1972" t="n">
         <v>-0.5157337576748295</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.492800816244275</v>
+        <v>2.554544814691455</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319548</v>
+        <v>3.819063300319549</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.816868806965215</v>
+        <v>2.878612805412395</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.309997334914017</v>
+        <v>-5.278348881599938</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.6925134486858608</v>
+        <v>0.7669168284586729</v>
       </c>
       <c r="F1973" t="n">
         <v>-0.5316230358078098</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.49789498548053</v>
+        <v>2.55963898392771</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489385</v>
+        <v>3.831819032489387</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.815404787789887</v>
+        <v>2.877148786237067</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.486335095036947</v>
+        <v>-5.454686641722867</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.620514325461361</v>
+        <v>0.6949177052341726</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.7079607959307392</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.390628310231444</v>
+        <v>2.452372308678624</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397796</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.813896405829816</v>
+        <v>2.875640404276996</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.485645722875724</v>
+        <v>-5.453997269561644</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.6192816923657785</v>
+        <v>0.6936850721385905</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.7079607959307392</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.389119928271373</v>
+        <v>2.450863926718553</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024963</v>
+        <v>3.836023391024964</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.813759273265252</v>
+        <v>2.875503271712432</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.492216687930316</v>
+        <v>-5.460568234616237</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.6165161737793778</v>
+        <v>0.6909195535521899</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.7145317609853321</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.385040216674053</v>
+        <v>2.446784215121233</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863225</v>
+        <v>3.821591150863227</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.813759273265252</v>
+        <v>2.875503271712432</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.484262717635544</v>
+        <v>-5.452614264321465</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.6196977618972865</v>
+        <v>0.6941011416700986</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.7145317609853321</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.385040216674053</v>
+        <v>2.446784215121233</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947585</v>
+        <v>3.833040181947586</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.820141030293057</v>
+        <v>2.881885028740236</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.473889341302457</v>
+        <v>-5.442240887988378</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.630228869458326</v>
+        <v>0.7046322492311381</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.7041583846522448</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.39764599950171</v>
+        <v>2.45938999794889</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326877</v>
+        <v>3.822707244326879</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.825033403667781</v>
+        <v>2.886777402114961</v>
       </c>
       <c r="D1979" t="n">
-        <v>-5.346205031508161</v>
+        <v>-5.314556578194082</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.6861949667507692</v>
+        <v>0.7605983465235813</v>
       </c>
       <c r="F1979" t="n">
         <v>-0.5764740748579483</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.479148958753013</v>
+        <v>2.540892957200193</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314553</v>
+        <v>3.828837911314555</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.811788076143654</v>
+        <v>2.873532074590833</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.406871621910549</v>
+        <v>-5.37522316859647</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.648683003065686</v>
+        <v>0.7230863828384981</v>
       </c>
       <c r="F1980" t="n">
         <v>-0.658172391576482</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.416884641197765</v>
+        <v>2.478628639644945</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690028</v>
+        <v>3.81686606769003</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.815885778754282</v>
+        <v>2.877629777201462</v>
       </c>
       <c r="D1981" t="n">
-        <v>-5.341877761976904</v>
+        <v>-5.310229308662825</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.6787782496497727</v>
+        <v>0.7531816294225848</v>
       </c>
       <c r="F1981" t="n">
         <v>-0.6313417769723266</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.437080712570887</v>
+        <v>2.498824711018067</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674311</v>
+        <v>3.817961388674313</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.82004671838536</v>
+        <v>2.88179071683254</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.442636397733902</v>
+        <v>-5.410987944419823</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.6426357349780516</v>
+        <v>0.7170391147508637</v>
       </c>
       <c r="F1982" t="n">
         <v>-0.7201673456993321</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.387946310965761</v>
+        <v>2.449690309412941</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.82671377916322</v>
+        <v>3.826713779163222</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.825926320913197</v>
+        <v>2.887670319360377</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.398433560648002</v>
+        <v>-5.366785107333922</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.6661964723402489</v>
+        <v>0.740599852113061</v>
       </c>
       <c r="F1983" t="n">
         <v>-0.6759645086134316</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.420347615745139</v>
+        <v>2.482091614192319</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022905</v>
+        <v>3.838228663022907</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.824336321382445</v>
+        <v>2.886080319829625</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.435412588311444</v>
+        <v>-5.403764134997365</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.6498148617441193</v>
+        <v>0.7242182415169314</v>
       </c>
       <c r="F1984" t="n">
         <v>-0.6389906068221011</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.440941957289184</v>
+        <v>2.502685955736364</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042139</v>
+        <v>3.863924114042141</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.875584086565484</v>
+        <v>2.937328085012664</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.455470667176285</v>
+        <v>-5.423822213862206</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.6930393953812231</v>
+        <v>0.7674427751540347</v>
       </c>
       <c r="F1985" t="n">
         <v>-0.6389906068221011</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.492189722472224</v>
+        <v>2.553933720919404</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86536771507828</v>
+        <v>3.865367715078282</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.874024791159738</v>
+        <v>2.935768789606918</v>
       </c>
       <c r="D1986" t="n">
-        <v>-5.415539993998395</v>
+        <v>-5.383891540684315</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.7074523692466324</v>
+        <v>0.781855749019444</v>
       </c>
       <c r="F1986" t="n">
         <v>-0.5990599336442107</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.514588830973212</v>
+        <v>2.576332829420392</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232396</v>
+        <v>3.864518876232398</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.868973019398008</v>
+        <v>2.930717017845188</v>
       </c>
       <c r="D1987" t="n">
-        <v>-5.37506964643569</v>
+        <v>-5.34342119312161</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.7185887365099841</v>
+        <v>0.7929921162827962</v>
       </c>
       <c r="F1987" t="n">
         <v>-0.5585895860815058</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.533819267749104</v>
+        <v>2.595563266196284</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162113</v>
+        <v>3.842576394162114</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.886160423490713</v>
+        <v>2.947904421937892</v>
       </c>
       <c r="D1988" t="n">
-        <v>-5.309845465308484</v>
+        <v>-5.278197011994405</v>
       </c>
       <c r="E1988" t="n">
-        <v>0.7618658130535714</v>
+        <v>0.836269192826383</v>
       </c>
       <c r="F1988" t="n">
         <v>-0.4933654049543001</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.590141180518133</v>
+        <v>2.651885178965313</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.782131786488418</v>
+        <v>3.80482204458267</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.812547058895741</v>
+        <v>2.899405547877594</v>
       </c>
       <c r="D1989" t="n">
-        <v>-5.309845465308484</v>
+        <v>-5.278197011994405</v>
       </c>
       <c r="E1989" t="n">
-        <v>0.7618658130535714</v>
+        <v>0.836269192826383</v>
       </c>
       <c r="F1989" t="n">
         <v>-0.4933654049543001</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.805610855882108</v>
+        <v>2.892469344863962</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240608.xlsx
+++ b/tame_output/ON/bt/strategyON_20240608.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>47.2%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-21.7%</t>
+          <t>-12.1%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.8%</t>
+          <t>-80.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.7%</t>
+          <t>108.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>128.2%</t>
+          <t>128.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>87.3%</t>
+          <t>87.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,12 +982,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-52.4%</t>
+          <t>-52.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.3%</t>
+          <t>-77.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.5%</t>
+          <t>452.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.4%</t>
+          <t>-10.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-689.4%</t>
+          <t>-679.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-28.7%</t>
+          <t>-28.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-292.6%</t>
+          <t>-288.7%</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-25.1%</t>
+          <t>-25.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-273.3%</t>
+          <t>-273.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>41.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.1%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-156.8%</t>
+          <t>-147.2%</t>
         </is>
       </c>
     </row>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097818</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094113</v>
+        <v>3.374439043094114</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017772</v>
+        <v>3.789311112017771</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839725</v>
+        <v>3.833252747839724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388728</v>
+        <v>3.839374447388727</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626473</v>
+        <v>3.856161751626472</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291811</v>
+        <v>3.78733042929181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.801637122785787</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390428</v>
+        <v>3.763182248390427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105952</v>
+        <v>3.784718794105951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960987</v>
+        <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607645</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710812</v>
+        <v>3.76033368671081</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409206</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.782922533493419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792047</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919908</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318094</v>
+        <v>3.748328408318092</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057527</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.8359579870115</v>
+        <v>3.835957987011498</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392989</v>
+        <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632783</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883075</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074784</v>
+        <v>3.798814771074782</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242294</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367686</v>
+        <v>3.821593509367684</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.892329249943547</v>
+        <v>-5.896813094834168</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6070238712855089</v>
+        <v>0.6052303333292604</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.9003254336242443</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879967</v>
+        <v>3.822326997879966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.839330927662159</v>
+        <v>-5.84381477255278</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6289017841154041</v>
+        <v>0.6271082461591555</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.8449891746223055</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861662650234</v>
+        <v>3.848616626502339</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.730526042182432</v>
+        <v>-5.735009887073053</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.6694218095272881</v>
+        <v>0.66762827157104</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.8449891746223055</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.81866895167594</v>
+        <v>3.818668951675939</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.510505244145421</v>
+        <v>-5.514989089036042</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.7590091657527065</v>
+        <v>0.7572156277964583</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.7037693295543253</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539952</v>
+        <v>3.84327452753995</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.377637555082144</v>
+        <v>-5.382121399972765</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.8280504241798408</v>
+        <v>0.8262568862235926</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.7037693295543253</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496264</v>
+        <v>3.845047386496262</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.218122451562774</v>
+        <v>-5.222606296453395</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.8930023100278905</v>
+        <v>0.8912087720716424</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.5442542260349553</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-5.073450306463037</v>
+        <v>-5.077934151353658</v>
       </c>
       <c r="E1932" t="n">
-        <v>0.9609592706292256</v>
+        <v>0.959165732672977</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.3995820809352179</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942104</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-5.133325133820729</v>
+        <v>-5.13780897871135</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9230468310875746</v>
+        <v>0.921253293131326</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.45945690829291</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674516</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-5.04652563604172</v>
+        <v>-5.051009480932342</v>
       </c>
       <c r="E1934" t="n">
-        <v>0.9801671235217442</v>
+        <v>0.9783735855654956</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.45945690829291</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430696</v>
+        <v>3.729146398430694</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-5.048995342503526</v>
+        <v>-5.053479187394148</v>
       </c>
       <c r="E1935" t="n">
-        <v>0.9792516423104338</v>
+        <v>0.9774581043541852</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.4619266147547162</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003604</v>
+        <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-5.117365528827536</v>
+        <v>-5.121849373718158</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.9629104902555321</v>
+        <v>0.9611169522992831</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.4526509157185012</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508372</v>
+        <v>3.71417913950837</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.22590370974367</v>
+        <v>-5.230387554634292</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9099319265209695</v>
+        <v>0.908138388564721</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.4526509157185012</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417705</v>
+        <v>3.710906731417703</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.256896869072375</v>
+        <v>-5.261380713962997</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.7222442278298744</v>
+        <v>0.7204506898736254</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.4526509157185012</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205901</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-5.081422609279906</v>
+        <v>-5.085906454170528</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.7970011637386496</v>
+        <v>0.795207625782401</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.4526509157185012</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225447</v>
+        <v>3.765024323225445</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-5.192358861921155</v>
+        <v>-5.196842706811777</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.7283686914433569</v>
+        <v>0.7265751534871083</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.4526509157185012</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111295</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.395385439464389</v>
+        <v>-5.39986928435501</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.6502894456459694</v>
+        <v>0.6484959076897208</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.6556774932617346</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-5.237459840529096</v>
+        <v>-5.241943685419717</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.7236320716522191</v>
+        <v>0.7218385336959701</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.6556774932617346</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-5.151216377502718</v>
+        <v>-5.15570022239334</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.7530757274366304</v>
+        <v>0.7512821894803814</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.6556774932617346</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316048</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-5.196523196901698</v>
+        <v>-5.20100704179232</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.7267287751215639</v>
+        <v>0.7249352371653153</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.6964876562709654</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-5.225556301603999</v>
+        <v>-5.230040146494621</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.7156674062737451</v>
+        <v>0.7138738683174961</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.6964876562709654</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809499</v>
+        <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-5.132745820153139</v>
+        <v>-5.137229665043761</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.6820642907454544</v>
+        <v>0.6802707527892058</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.6036771748201061</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-5.177135289482567</v>
+        <v>-5.181619134373189</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.6661819789382846</v>
+        <v>0.6643884409820355</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.6480666441495337</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472739</v>
+        <v>3.721077195472737</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-5.064464071246316</v>
+        <v>-5.068947916136938</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.7063261747445075</v>
+        <v>0.7045326367882585</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.5353954259132836</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798538</v>
+        <v>3.743047603798536</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.952087070063643</v>
+        <v>-4.956570914954265</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.756768271048244</v>
+        <v>0.7549747330919951</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.5353954259132836</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498866</v>
+        <v>3.689597840498864</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-5.150321638950374</v>
+        <v>-5.154805483840996</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.6889716452620904</v>
+        <v>0.6871781073058418</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.7336299948000142</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705326</v>
+        <v>3.643069621705324</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-5.233322919975653</v>
+        <v>-5.237806764866275</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.4941268528526321</v>
+        <v>0.4923333148963835</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.7522008793271879</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729271</v>
+        <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-5.341936998418984</v>
+        <v>-5.346420843309606</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.5708308821945054</v>
+        <v>0.5690373442382568</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.7522008793271879</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.73301244119077</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.428535581400087</v>
+        <v>-5.433019426290709</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.5507044751043875</v>
+        <v>0.5489109371481384</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.7522008793271879</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.390151918841936</v>
+        <v>-5.394635763732558</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.5634773814700162</v>
+        <v>0.5616838435137677</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.7138172167690368</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532485</v>
+        <v>3.751147197532483</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-5.21303558880677</v>
+        <v>-5.217519433697392</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.6310529423293847</v>
+        <v>0.6292594043731361</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.7138172167690368</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-5.258127833640316</v>
+        <v>-5.262611678530938</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.6136994361578796</v>
+        <v>0.611905898201631</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.7757132599384265</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011236</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-5.078752412401548</v>
+        <v>-5.08323625729217</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.679236579959801</v>
+        <v>0.6774430420035524</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.6189365017677079</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982231</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-5.123766625922155</v>
+        <v>-5.128250470812777</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.6420383498831481</v>
+        <v>0.6402448119268995</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.6492853970823125</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509538</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.39077113619459</v>
+        <v>-5.395254981085212</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.5409281081131199</v>
+        <v>0.5391345701568713</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.8436484351252611</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.491968917631763</v>
+        <v>-5.496452762522384</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.4996529174347524</v>
+        <v>0.4978593794785033</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.9120572486705802</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815456</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.45949333146099</v>
+        <v>-5.463977176351612</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.5102431134573777</v>
+        <v>0.5084495755011291</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.9120572486705802</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.440455203753693</v>
+        <v>-5.444939048644315</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.5143830837485415</v>
+        <v>0.5125895457922929</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.9702408600017748</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131252</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.471581834904311</v>
+        <v>-5.476065679794933</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.679514300226975</v>
+        <v>0.677720762270726</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.9702408600017748</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067868</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.523902215505103</v>
+        <v>-5.528386060395725</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.6594194769727917</v>
+        <v>0.6576259390165431</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.9352939999929026</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789125</v>
+        <v>3.787425580789123</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.544159514034061</v>
+        <v>-5.548643358924683</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.6573250879581343</v>
+        <v>0.6555315500018857</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.9352939999929026</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.78150125051991</v>
+        <v>3.781501250519908</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.396416543799059</v>
+        <v>-5.40090038868968</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.7955749238441574</v>
+        <v>0.7937813858879088</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.7674866427580195</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181173</v>
+        <v>3.802245929181171</v>
       </c>
       <c r="C1967" t="n">
         <v>3.019035585656189</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.49843122633028</v>
+        <v>-5.396447902131258</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8193066708103296</v>
+        <v>0.8601000004899384</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.7674866427580195</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.80560898539473</v>
       </c>
       <c r="C1968" t="n">
         <v>3.019697934047847</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.361821882236187</v>
+        <v>-5.259838558037165</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8746127568396251</v>
+        <v>0.9154060865192339</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.6308772986639271</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890612</v>
       </c>
       <c r="C1969" t="n">
         <v>3.018778410787958</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.504587215058837</v>
+        <v>-5.402603890859815</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8165871004506755</v>
+        <v>0.8573804301302843</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.7736426314865774</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798428</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>3.085113964584778</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.442289216282715</v>
+        <v>-5.340305892083693</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9078418537579451</v>
+        <v>0.9486351834375539</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.7736426314865774</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992193</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
         <v>2.793694836974177</v>
       </c>
       <c r="D1971" t="n">
-        <v>-5.240499018617557</v>
+        <v>-5.138515694418535</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.6971388052134064</v>
+        <v>0.7379321348930152</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.575624439317423</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852425</v>
+        <v>3.841444817852422</v>
       </c>
       <c r="C1972" t="n">
         <v>2.863985069296352</v>
       </c>
       <c r="D1972" t="n">
-        <v>-5.180608336974964</v>
+        <v>-5.078625012775942</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.7913853101926192</v>
+        <v>0.832178639872228</v>
       </c>
       <c r="F1972" t="n">
         <v>-0.5157337576748295</v>
@@ -46924,16 +46924,16 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319549</v>
+        <v>3.819063300319546</v>
       </c>
       <c r="C1973" t="n">
         <v>2.878612805412395</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.278348881599938</v>
+        <v>-5.176365557400916</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.7669168284586729</v>
+        <v>0.8077101581382817</v>
       </c>
       <c r="F1973" t="n">
         <v>-0.5316230358078098</v>
@@ -46947,16 +46947,16 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489387</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
         <v>2.877148786237067</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.454686641722867</v>
+        <v>-5.352703317523845</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.6949177052341726</v>
+        <v>0.7357110349137814</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.7079607959307392</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397796</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.875640404276996</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.453997269561644</v>
+        <v>-5.352013945362622</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.6936850721385905</v>
+        <v>0.7344784018181993</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.7079607959307392</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024964</v>
+        <v>3.836023391024961</v>
       </c>
       <c r="C1976" t="n">
         <v>2.875503271712432</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.460568234616237</v>
+        <v>-5.358584910417215</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.6909195535521899</v>
+        <v>0.7317128832317987</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.7145317609853321</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863227</v>
+        <v>3.821591150863223</v>
       </c>
       <c r="C1977" t="n">
         <v>2.875503271712432</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.452614264321465</v>
+        <v>-5.350630940122443</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.6941011416700986</v>
+        <v>0.7348944713497074</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.7145317609853321</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947586</v>
+        <v>3.833040181947583</v>
       </c>
       <c r="C1978" t="n">
         <v>2.881885028740236</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.442240887988378</v>
+        <v>-5.340257563789356</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.7046322492311381</v>
+        <v>0.7454255789107469</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.7041583846522448</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326879</v>
+        <v>3.822707244326875</v>
       </c>
       <c r="C1979" t="n">
         <v>2.886777402114961</v>
       </c>
       <c r="D1979" t="n">
-        <v>-5.314556578194082</v>
+        <v>-5.21257325399506</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.7605983465235813</v>
+        <v>0.8013916762031901</v>
       </c>
       <c r="F1979" t="n">
         <v>-0.5764740748579483</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314555</v>
+        <v>3.828837911314551</v>
       </c>
       <c r="C1980" t="n">
         <v>2.873532074590833</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.37522316859647</v>
+        <v>-5.273239844397448</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.7230863828384981</v>
+        <v>0.7638797125181069</v>
       </c>
       <c r="F1980" t="n">
         <v>-0.658172391576482</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.81686606769003</v>
+        <v>3.816866067690026</v>
       </c>
       <c r="C1981" t="n">
         <v>2.877629777201462</v>
       </c>
       <c r="D1981" t="n">
-        <v>-5.310229308662825</v>
+        <v>-5.208245984463803</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.7531816294225848</v>
+        <v>0.7939749591021936</v>
       </c>
       <c r="F1981" t="n">
         <v>-0.6313417769723266</v>
@@ -47131,16 +47131,16 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674313</v>
+        <v>3.817961388674309</v>
       </c>
       <c r="C1982" t="n">
         <v>2.88179071683254</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.410987944419823</v>
+        <v>-5.309004620220801</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.7170391147508637</v>
+        <v>0.7578324444304725</v>
       </c>
       <c r="F1982" t="n">
         <v>-0.7201673456993321</v>
@@ -47154,16 +47154,16 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163222</v>
+        <v>3.826713779163218</v>
       </c>
       <c r="C1983" t="n">
         <v>2.887670319360377</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.366785107333922</v>
+        <v>-5.2648017831349</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.740599852113061</v>
+        <v>0.7813931817926698</v>
       </c>
       <c r="F1983" t="n">
         <v>-0.6759645086134316</v>
@@ -47177,16 +47177,16 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022907</v>
+        <v>3.838228663022903</v>
       </c>
       <c r="C1984" t="n">
         <v>2.886080319829625</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.403764134997365</v>
+        <v>-5.301780810798343</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.7242182415169314</v>
+        <v>0.7650115711965402</v>
       </c>
       <c r="F1984" t="n">
         <v>-0.6389906068221011</v>
@@ -47200,16 +47200,16 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042141</v>
+        <v>3.863924114042137</v>
       </c>
       <c r="C1985" t="n">
         <v>2.937328085012664</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.423822213862206</v>
+        <v>-5.321838889663184</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.7674427751540347</v>
+        <v>0.8082361048336435</v>
       </c>
       <c r="F1985" t="n">
         <v>-0.6389906068221011</v>
@@ -47223,16 +47223,16 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078282</v>
+        <v>3.865367715078278</v>
       </c>
       <c r="C1986" t="n">
         <v>2.935768789606918</v>
       </c>
       <c r="D1986" t="n">
-        <v>-5.383891540684315</v>
+        <v>-5.281908216485293</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.781855749019444</v>
+        <v>0.8226490786990528</v>
       </c>
       <c r="F1986" t="n">
         <v>-0.5990599336442107</v>
@@ -47246,16 +47246,16 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232398</v>
+        <v>3.864518876232395</v>
       </c>
       <c r="C1987" t="n">
         <v>2.930717017845188</v>
       </c>
       <c r="D1987" t="n">
-        <v>-5.34342119312161</v>
+        <v>-5.241437868922588</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.7929921162827962</v>
+        <v>0.833785445962405</v>
       </c>
       <c r="F1987" t="n">
         <v>-0.5585895860815058</v>
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162114</v>
+        <v>3.84257639416211</v>
       </c>
       <c r="C1988" t="n">
         <v>2.947904421937892</v>
       </c>
       <c r="D1988" t="n">
-        <v>-5.278197011994405</v>
+        <v>-5.180902659420321</v>
       </c>
       <c r="E1988" t="n">
-        <v>0.836269192826383</v>
+        <v>0.8751869338560168</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.4933654049543001</v>
+        <v>-0.4980543765792376</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.651885178965313</v>
+        <v>2.64907179599035</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.80482204458267</v>
+        <v>3.752318011860002</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.899405547877594</v>
+        <v>2.995429503332813</v>
       </c>
       <c r="D1989" t="n">
-        <v>-5.278197011994405</v>
+        <v>-5.180902659420321</v>
       </c>
       <c r="E1989" t="n">
-        <v>0.836269192826383</v>
+        <v>0.8751869338560168</v>
       </c>
       <c r="F1989" t="n">
-        <v>-0.4933654049543001</v>
+        <v>-0.4980543765792376</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.892469344863962</v>
+        <v>2.988493300319181</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240608.xlsx
+++ b/tame_output/ON/bt/strategyON_20240608.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>18.3%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.7%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-12.1%</t>
+          <t>-28.7%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.4%</t>
+          <t>-80.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.6%</t>
+          <t>108.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>128.1%</t>
+          <t>128.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>87.2%</t>
+          <t>87.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,22 +982,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-52.0%</t>
+          <t>-53.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.0%</t>
+          <t>-77.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.1%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>452.8%</t>
+          <t>449.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.6%</t>
+          <t>-10.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-679.7%</t>
+          <t>-692.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,37 +1140,37 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-42.0%</t>
+          <t>-39.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-28.5%</t>
+          <t>-27.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-288.7%</t>
+          <t>-305.7%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-31.0%</t>
+          <t>-33.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>70.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-34.4%</t>
+          <t>-33.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-25.2%</t>
+          <t>-28.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.5%</t>
+          <t>-155.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-273.8%</t>
+          <t>-295.7%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>41.6%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-147.2%</t>
+          <t>-206.1%</t>
         </is>
       </c>
     </row>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108636</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097818</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094114</v>
+        <v>3.374439043094113</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199283</v>
+        <v>3.405960511199282</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969591</v>
+        <v>3.42463335496959</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923085</v>
+        <v>3.419979433923084</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297748</v>
+        <v>3.458100091297747</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317614</v>
+        <v>3.447750501317613</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737167</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.50317028234131</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539461</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.5027903991417</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.48587859441027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940719</v>
+        <v>3.691571733940718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.67684154977058</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812103</v>
+        <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646217</v>
+        <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311947</v>
+        <v>3.784684521311946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017771</v>
+        <v>3.78931111201777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839724</v>
+        <v>3.833252747839723</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388727</v>
+        <v>3.839374447388726</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626472</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78733042929181</v>
+        <v>3.787330429291809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785787</v>
+        <v>3.801637122785786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390427</v>
+        <v>3.763182248390426</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960986</v>
+        <v>3.753882571960985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45849,10 +45849,10 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.896813094834168</v>
+        <v>-5.901960469358577</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6052303333292604</v>
+        <v>0.6031713835194967</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.9003254336242443</v>
@@ -45872,10 +45872,10 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.84381477255278</v>
+        <v>-5.848962147077189</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6271082461591555</v>
+        <v>0.6250492963493919</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.8449891746223055</v>
@@ -45895,10 +45895,10 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.735009887073053</v>
+        <v>-5.740157261597462</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.66762827157104</v>
+        <v>0.6655693217612764</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.8449891746223055</v>
@@ -45918,10 +45918,10 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.514989089036042</v>
+        <v>-5.520136463560451</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.7572156277964583</v>
+        <v>0.7551566779866947</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.7037693295543253</v>
@@ -45941,10 +45941,10 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.382121399972765</v>
+        <v>-5.387268774497174</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.8262568862235926</v>
+        <v>0.824197936413829</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.7037693295543253</v>
@@ -45964,10 +45964,10 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.222606296453395</v>
+        <v>-5.227753670977804</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.8912087720716424</v>
+        <v>0.8891498222618788</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.5442542260349553</v>
@@ -45987,10 +45987,10 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-5.077934151353658</v>
+        <v>-5.083081525878066</v>
       </c>
       <c r="E1932" t="n">
-        <v>0.959165732672977</v>
+        <v>0.9571067828632138</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.3995820809352179</v>
@@ -46010,10 +46010,10 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-5.13780897871135</v>
+        <v>-5.142956353235759</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.921253293131326</v>
+        <v>0.9191943433215624</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.45945690829291</v>
@@ -46033,10 +46033,10 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-5.051009480932342</v>
+        <v>-5.05615685545675</v>
       </c>
       <c r="E1934" t="n">
-        <v>0.9783735855654956</v>
+        <v>0.976314635755732</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.45945690829291</v>
@@ -46056,10 +46056,10 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-5.053479187394148</v>
+        <v>-5.058626561918556</v>
       </c>
       <c r="E1935" t="n">
-        <v>0.9774581043541852</v>
+        <v>0.9753991545444216</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.4619266147547162</v>
@@ -46079,10 +46079,10 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-5.121849373718158</v>
+        <v>-5.126996748242567</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.9611169522992831</v>
+        <v>0.9590580024895194</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.4526509157185012</v>
@@ -46102,10 +46102,10 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.230387554634292</v>
+        <v>-5.235534929158701</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.908138388564721</v>
+        <v>0.9060794387549573</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.4526509157185012</v>
@@ -46125,10 +46125,10 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.261380713962997</v>
+        <v>-5.266528088487406</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.7204506898736254</v>
+        <v>0.7183917400638622</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.4526509157185012</v>
@@ -46148,10 +46148,10 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-5.085906454170528</v>
+        <v>-5.091053828694937</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.795207625782401</v>
+        <v>0.7931486759726374</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.4526509157185012</v>
@@ -46171,10 +46171,10 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-5.196842706811777</v>
+        <v>-5.201990081336186</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.7265751534871083</v>
+        <v>0.7245162036773447</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.4526509157185012</v>
@@ -46194,10 +46194,10 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.39986928435501</v>
+        <v>-5.405016658879419</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.6484959076897208</v>
+        <v>0.6464369578799571</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.6556774932617346</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264163</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-5.241943685419717</v>
+        <v>-5.247091059944126</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.7218385336959701</v>
+        <v>0.7197795838862064</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.6556774932617346</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-5.15570022239334</v>
+        <v>-5.160847596917749</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.7512821894803814</v>
+        <v>0.7492232396706182</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.6556774932617346</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316047</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-5.20100704179232</v>
+        <v>-5.206154416316728</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.7249352371653153</v>
+        <v>0.7228762873555516</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.6964876562709654</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-5.230040146494621</v>
+        <v>-5.23518752101903</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.7138738683174961</v>
+        <v>0.7118149185077329</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.6964876562709654</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809497</v>
+        <v>3.733390600809498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-5.137229665043761</v>
+        <v>-5.14237703956817</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.6802707527892058</v>
+        <v>0.6782118029794422</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.6036771748201061</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560425</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-5.181619134373189</v>
+        <v>-5.186766508897597</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.6643884409820355</v>
+        <v>0.6623294911722719</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.6480666441495337</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472737</v>
+        <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-5.068947916136938</v>
+        <v>-5.074095290661347</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.7045326367882585</v>
+        <v>0.7024736869784953</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.5353954259132836</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798536</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.956570914954265</v>
+        <v>-4.961718289478674</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.7549747330919951</v>
+        <v>0.7529157832822315</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.5353954259132836</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498864</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-5.154805483840996</v>
+        <v>-5.159952858365405</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.6871781073058418</v>
+        <v>0.6851191574960782</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.7336299948000142</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705324</v>
+        <v>3.643069621705325</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-5.237806764866275</v>
+        <v>-5.242954139390684</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.4923333148963835</v>
+        <v>0.4902743650866199</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.7522008793271879</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729269</v>
+        <v>3.68271631072927</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-5.346420843309606</v>
+        <v>-5.351568217834015</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.5690373442382568</v>
+        <v>0.5669783944284932</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.7522008793271879</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.733012441190769</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.433019426290709</v>
+        <v>-5.438166800815118</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.5489109371481384</v>
+        <v>0.5468519873383748</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.7522008793271879</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.394635763732558</v>
+        <v>-5.399783138256967</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.5616838435137677</v>
+        <v>0.559624893704004</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.7138172167690368</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532483</v>
+        <v>3.751147197532485</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-5.217519433697392</v>
+        <v>-5.222666808221801</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.6292594043731361</v>
+        <v>0.6272004545633725</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.7138172167690368</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-5.262611678530938</v>
+        <v>-5.267759053055347</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.611905898201631</v>
+        <v>0.6098469483918674</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.7757132599384265</v>
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011235</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-5.08323625729217</v>
+        <v>-5.28760851391139</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.6774430420035524</v>
+        <v>0.5956941393558646</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.6189365017677079</v>
+        <v>-0.8298857378335189</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.339732068173543</v>
+        <v>2.213162526534057</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.71699171898223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-5.128250470812777</v>
+        <v>-5.332622727431996</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.6402448119268995</v>
+        <v>0.5584959092792117</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.6492853970823125</v>
+        <v>-0.8602346331481235</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.30233018631637</v>
+        <v>2.175760644676884</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509537</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.395254981085212</v>
+        <v>-5.599627237704431</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.5391345701568713</v>
+        <v>0.4573856675091834</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.8436484351252611</v>
+        <v>-1.054597671191072</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.191403925829547</v>
+        <v>2.06483438419006</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760811</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.496452762522384</v>
+        <v>-5.700825019141604</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.4978593794785033</v>
+        <v>0.4161104768308155</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.9120572486705802</v>
+        <v>-1.123006484736391</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.149562559598857</v>
+        <v>2.02299301795937</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815456</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.463977176351612</v>
+        <v>-5.668349432970832</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.5084495755011291</v>
+        <v>0.4267006728534413</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.9120572486705802</v>
+        <v>-1.123006484736391</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.147162521153174</v>
+        <v>2.020592979513687</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378101</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.444939048644315</v>
+        <v>-5.649311305263534</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.5125895457922929</v>
+        <v>0.430840643144605</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.9702408600017748</v>
+        <v>-1.181190096067586</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.108777073562702</v>
+        <v>1.982207531923215</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.476065679794933</v>
+        <v>-5.680437936414153</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.677720762270726</v>
+        <v>0.5959718596230381</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.9702408600017748</v>
+        <v>-1.181190096067586</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.286358942501382</v>
+        <v>2.159789400861896</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067867</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.528386060395725</v>
+        <v>-5.732758317014945</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.6576259390165431</v>
+        <v>0.5758770363688552</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.9352939999929026</v>
+        <v>-1.146243236058713</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.308160387492839</v>
+        <v>2.181590845853353</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789123</v>
+        <v>3.787425580789124</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.548643358924683</v>
+        <v>-5.753015615543903</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.6555315500018857</v>
+        <v>0.5737826473541978</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.9352939999929026</v>
+        <v>-1.146243236058713</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.314168917889765</v>
+        <v>2.187599376250279</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519908</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.40090038868968</v>
+        <v>-5.6052726453089</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.7937813858879088</v>
+        <v>0.7120324832402209</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.7674866427580195</v>
+        <v>-0.9784358788238302</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.494005980022717</v>
+        <v>2.36743643838323</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181171</v>
+        <v>3.802245929181172</v>
       </c>
       <c r="C1967" t="n">
-        <v>3.019035585656189</v>
+        <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.396447902131258</v>
+        <v>-5.707287327840121</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8601000004899384</v>
+        <v>0.6740202317592132</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.7674866427580195</v>
+        <v>-0.9784358788238302</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.558543600001378</v>
+        <v>2.370230059914711</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560898539473</v>
+        <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
-        <v>3.019697934047847</v>
+        <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.259838558037165</v>
+        <v>-5.570677983746029</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9154060865192339</v>
+        <v>0.7293263177885088</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.6308772986639271</v>
+        <v>-0.8418265347297378</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.641171554849492</v>
+        <v>2.452858014762825</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890612</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
-        <v>3.018778410787958</v>
+        <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.402603890859815</v>
+        <v>-5.713443316568679</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8573804301302843</v>
+        <v>0.6713006613995591</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.7736426314865774</v>
+        <v>-0.9845918675523881</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.554592831896012</v>
+        <v>2.366279291809345</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.085113964584778</v>
+        <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.340305892083693</v>
+        <v>-5.651145317792556</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9486351834375539</v>
+        <v>0.7625554147068287</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.7736426314865774</v>
+        <v>-0.9845918675523881</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.620928385692832</v>
+        <v>2.432614845606166</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.848729139992192</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.793694836974177</v>
+        <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-5.138515694418535</v>
+        <v>-5.449355120127398</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.7379321348930152</v>
+        <v>0.5518523661622901</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.575624439317423</v>
+        <v>-0.7865736753832338</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.448320173383723</v>
+        <v>2.260006633297057</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852422</v>
+        <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.863985069296352</v>
+        <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-5.078625012775942</v>
+        <v>-5.389464438484805</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.832178639872228</v>
+        <v>0.6460988711415023</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.5157337576748295</v>
+        <v>-0.7266829937406403</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.554544814691455</v>
+        <v>2.366231274604788</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319546</v>
+        <v>3.819063300319548</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.878612805412395</v>
+        <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.176365557400916</v>
+        <v>-5.48720498310978</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8077101581382817</v>
+        <v>0.6216303894075565</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.5316230358078098</v>
+        <v>-0.7425722718736205</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.55963898392771</v>
+        <v>2.371325443841044</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.877148786237067</v>
+        <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.352703317523845</v>
+        <v>-5.663542743232709</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.7357110349137814</v>
+        <v>0.5496312661830562</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.7079607959307392</v>
+        <v>-0.91891003199655</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.452372308678624</v>
+        <v>2.264058768591958</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.875640404276996</v>
+        <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.352013945362622</v>
+        <v>-5.662853371071486</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.7344784018181993</v>
+        <v>0.5483986330874742</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.7079607959307392</v>
+        <v>-0.91891003199655</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.450863926718553</v>
+        <v>2.262550386631886</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024961</v>
+        <v>3.836023391024963</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.875503271712432</v>
+        <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.358584910417215</v>
+        <v>-5.669424336126078</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.7317128832317987</v>
+        <v>0.5456331145010731</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.7145317609853321</v>
+        <v>-0.9254809970511428</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.446784215121233</v>
+        <v>2.258470675034566</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863223</v>
+        <v>3.821591150863225</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.875503271712432</v>
+        <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.350630940122443</v>
+        <v>-5.661470365831306</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.7348944713497074</v>
+        <v>0.5488147026189822</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.7145317609853321</v>
+        <v>-0.9254809970511428</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.446784215121233</v>
+        <v>2.258470675034566</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947583</v>
+        <v>3.833040181947585</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.881885028740236</v>
+        <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.340257563789356</v>
+        <v>-5.651096989498219</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.7454255789107469</v>
+        <v>0.5593458101800217</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.7041583846522448</v>
+        <v>-0.9151076207180555</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.45938999794889</v>
+        <v>2.271076457862224</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326875</v>
+        <v>3.822707244326877</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.886777402114961</v>
+        <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-5.21257325399506</v>
+        <v>-5.523412679703923</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.8013916762031901</v>
+        <v>0.6153119074724649</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.5764740748579483</v>
+        <v>-0.7874233109237591</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.540892957200193</v>
+        <v>2.352579417113526</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314551</v>
+        <v>3.828837911314553</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.873532074590833</v>
+        <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.273239844397448</v>
+        <v>-5.584079270106312</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.7638797125181069</v>
+        <v>0.5777999437873818</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.658172391576482</v>
+        <v>-0.8691216276422927</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.478628639644945</v>
+        <v>2.290315099558279</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690026</v>
+        <v>3.816866067690028</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.877629777201462</v>
+        <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-5.208245984463803</v>
+        <v>-5.519085410172666</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.7939749591021936</v>
+        <v>0.6078951903714684</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.6313417769723266</v>
+        <v>-0.8422910130381374</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.498824711018067</v>
+        <v>2.3105111709314</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674309</v>
+        <v>3.817961388674311</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.88179071683254</v>
+        <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.309004620220801</v>
+        <v>-5.619844045929664</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.7578324444304725</v>
+        <v>0.5717526756997473</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.7201673456993321</v>
+        <v>-0.9311165817651428</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.449690309412941</v>
+        <v>2.261376769326275</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163218</v>
+        <v>3.82671377916322</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.887670319360377</v>
+        <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.2648017831349</v>
+        <v>-5.575641208843764</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.7813931817926698</v>
+        <v>0.5953134130619446</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.6759645086134316</v>
+        <v>-0.8869137446792423</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.482091614192319</v>
+        <v>2.293778074105652</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022903</v>
+        <v>3.838228663022905</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.886080319829625</v>
+        <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.301780810798343</v>
+        <v>-5.612620236507206</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.7650115711965402</v>
+        <v>0.578931802465815</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.6389906068221011</v>
+        <v>-0.8499398428879118</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.502685955736364</v>
+        <v>2.314372415649698</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042137</v>
+        <v>3.863924114042139</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.937328085012664</v>
+        <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.321838889663184</v>
+        <v>-5.632678315372047</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.8082361048336435</v>
+        <v>0.6221563361029183</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.6389906068221011</v>
+        <v>-0.8499398428879118</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.553933720919404</v>
+        <v>2.365620180832738</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078278</v>
+        <v>3.86536771507828</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.935768789606918</v>
+        <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-5.281908216485293</v>
+        <v>-5.592747642194157</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.8226490786990528</v>
+        <v>0.6365693099683276</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.5990599336442107</v>
+        <v>-0.8100091697100215</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.576332829420392</v>
+        <v>2.388019289333725</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232395</v>
+        <v>3.864518876232396</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.930717017845188</v>
+        <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-5.241437868922588</v>
+        <v>-5.552277294631452</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.833785445962405</v>
+        <v>0.6477056772316798</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.5585895860815058</v>
+        <v>-0.7695388221473165</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.595563266196284</v>
+        <v>2.407249726109618</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.84257639416211</v>
+        <v>3.842576394162111</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.947904421937892</v>
+        <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-5.180902659420321</v>
+        <v>-5.487053113504246</v>
       </c>
       <c r="E1988" t="n">
-        <v>0.8751869338560168</v>
+        <v>0.6909827537752666</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.4980543765792376</v>
+        <v>-0.7043146410201109</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.64907179599035</v>
+        <v>2.463571638878646</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.752318011860002</v>
+        <v>3.463312654099892</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.995429503332813</v>
+        <v>2.829633952372269</v>
       </c>
       <c r="D1989" t="n">
-        <v>-5.180902659420321</v>
+        <v>-5.310382276877781</v>
       </c>
       <c r="E1989" t="n">
-        <v>0.8751869338560168</v>
+        <v>0.7051246173074097</v>
       </c>
       <c r="F1989" t="n">
-        <v>-0.4980543765792376</v>
+        <v>-0.7166928877733576</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.988493300319181</v>
+        <v>2.399618219708255</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240608.xlsx
+++ b/tame_output/ON/bt/strategyON_20240608.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.8%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>57.2%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-28.7%</t>
+          <t>-23.4%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.9%</t>
+          <t>-80.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.7%</t>
+          <t>108.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>128.2%</t>
+          <t>127.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-53.1%</t>
+          <t>-50.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.5%</t>
+          <t>-77.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>449.1%</t>
+          <t>453.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.4%</t>
+          <t>-10.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-692.6%</t>
+          <t>-689.9%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,32 +1140,32 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-39.5%</t>
+          <t>-41.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-27.8%</t>
+          <t>-26.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-6.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-305.7%</t>
+          <t>-299.4%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-33.6%</t>
+          <t>-31.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.1%</t>
+          <t>-34.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-28.8%</t>
+          <t>-25.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.1%</t>
+          <t>-157.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-295.7%</t>
+          <t>-277.8%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,12 +1400,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.1%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-206.1%</t>
+          <t>-190.1%</t>
         </is>
       </c>
     </row>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097818</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.792600906165847</v>
+        <v>-7.746755052717844</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.001481906912602859</v>
+        <v>0.01982024829180373</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.624412880725885</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094113</v>
+        <v>3.374439043094114</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.138475728150656</v>
+        <v>-8.092629874702652</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1407684567356258</v>
+        <v>-0.1224301153564245</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.624412880725885</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199282</v>
+        <v>3.405960511199283</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.30205560633504</v>
+        <v>-8.256209752887036</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2077954879543786</v>
+        <v>-0.1894571465751773</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.624412880725885</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.42463335496959</v>
+        <v>3.424633354969591</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.598716948145238</v>
+        <v>-8.552871094697235</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3226810487492497</v>
+        <v>-0.3043427073700484</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.693156016459764</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923084</v>
+        <v>3.419979433923085</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.803748128919555</v>
+        <v>-8.757902275471551</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.4087198255933795</v>
+        <v>-0.3903814842141777</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.693156016459764</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297747</v>
+        <v>3.458100091297748</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.186749517662186</v>
+        <v>-9.140903664214182</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5620224824120159</v>
+        <v>-0.5436841410328146</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.693156016459764</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317613</v>
+        <v>3.447750501317614</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.36861930864722</v>
+        <v>-9.322773455199217</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.6321988828345995</v>
+        <v>-0.6138605414553981</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.875025807444799</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737167</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.728149631151222</v>
+        <v>-9.682303777703218</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7706607085381503</v>
+        <v>-0.7523223671589485</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.875025807444799</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.50317028234131</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.778498694605444</v>
+        <v>-9.73265284115744</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7828843139626613</v>
+        <v>-0.76454597258346</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.925374870899021</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539461</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.87611797202684</v>
+        <v>-9.830272118578836</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.8188902743094508</v>
+        <v>-0.8005519329302495</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.022994148320417</v>
@@ -44722,10 +44722,10 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.02364406003248</v>
+        <v>-9.977798206584479</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8750071531901358</v>
+        <v>-0.8566688118109345</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.170520236326061</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.5027903991417</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.22790223536235</v>
+        <v>-10.18205638191434</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.9511972262034387</v>
+        <v>-0.9328588848242374</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.29815918094005</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.36971200956913</v>
+        <v>-10.32386615612113</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.003438581401718</v>
+        <v>-0.9851002400225171</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.469437978585626</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440633</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.29624217790169</v>
+        <v>-10.25039632445368</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.9586789472413173</v>
+        <v>-0.940340605862116</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.395968146918177</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.47136659528823</v>
+        <v>-10.42552074184023</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.014173493448418</v>
+        <v>-0.9958351520692164</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.571092564304721</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587859441027</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.70581868930272</v>
+        <v>-10.65997283585472</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.11517349595581</v>
+        <v>-1.096835154576608</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.571092564304721</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764395</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.99362253383996</v>
+        <v>-10.94777668039195</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.236967224544682</v>
+        <v>-1.21862888316548</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.858896408841959</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390584</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.04640868944028</v>
+        <v>-11.00056283599228</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.256965896946256</v>
+        <v>-1.238627555567055</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.954571895424356</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.17244548280857</v>
+        <v>-11.12659962936057</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.304686885664457</v>
+        <v>-1.286348544285256</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.929320272614614</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.12042996883976</v>
+        <v>-11.07458411539176</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.279890344390531</v>
+        <v>-1.261552003011329</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.929320272614614</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.26210181056388</v>
+        <v>-11.21625595711588</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.338034307978921</v>
+        <v>-1.319695966599719</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.929320272614614</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940718</v>
+        <v>3.691571733940719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.21251096613905</v>
+        <v>-11.16666511269104</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.303144560044114</v>
+        <v>-1.284806218664913</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.87972942818978</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.67684154977058</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.19970357313427</v>
+        <v>-11.15385771968627</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.311072736488888</v>
+        <v>-1.292734395109686</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.928585203198681</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.97385842041486</v>
+        <v>-10.92801256696686</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.211155602364915</v>
+        <v>-1.192817260985713</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.886658527611517</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.684843823812103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.84927976407727</v>
+        <v>-10.80343391062926</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.160184995273819</v>
+        <v>-1.141846653894617</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.886658527611517</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.90217505212155</v>
+        <v>-10.85632919867355</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.178709336329426</v>
+        <v>-1.160370994950225</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.881703181523071</v>
@@ -45090,10 +45090,10 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.83004187683367</v>
+        <v>-10.78419602338567</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.144122361975637</v>
+        <v>-1.125784020596435</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.881703181523071</v>
@@ -45113,10 +45113,10 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.75867548422403</v>
+        <v>-10.71282963077602</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.125313067325643</v>
+        <v>-1.106974725946442</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.810336788913423</v>
@@ -45136,10 +45136,10 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.49483861701996</v>
+        <v>-10.44899276357195</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.029661801756923</v>
+        <v>-1.011323460377721</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.810336788913423</v>
@@ -45159,10 +45159,10 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.22759681615156</v>
+        <v>-10.18175096270356</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.9245996419089377</v>
+        <v>-0.9062613005297364</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.810336788913423</v>
@@ -45182,10 +45182,10 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.12968977747507</v>
+        <v>-10.08384392402706</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8857371414118025</v>
+        <v>-0.8673988000326003</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.742351039052866</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097241</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.10573623649911</v>
+        <v>-10.05989038305111</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8754872188759255</v>
+        <v>-0.8571488774967242</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.718397498076909</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78931111201777</v>
+        <v>3.789311112017771</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.841676298176314</v>
+        <v>-9.79583044472831</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7831235597085588</v>
+        <v>-0.7647852183293571</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.454337559754113</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839723</v>
+        <v>3.833252747839724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.134596674671476</v>
+        <v>-9.088750821223472</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.5030787439669249</v>
+        <v>-0.4847404025877231</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.454337559754113</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388726</v>
+        <v>3.839374447388727</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.094412376305286</v>
+        <v>-9.048566522857282</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.4866614007326073</v>
+        <v>-0.4683230593534056</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.414153261387922</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.856161751626472</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.014342580767481</v>
+        <v>-8.968496727319478</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.4552666612967284</v>
+        <v>-0.4369283199175271</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.334083465850118</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291809</v>
+        <v>3.78733042929181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.780861358537884</v>
+        <v>-8.73501550508988</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.3539497435670369</v>
+        <v>-0.3356114021878356</v>
       </c>
       <c r="F1903" t="n">
         <v>-2.100602243620519</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785786</v>
+        <v>3.801637122785787</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.631194967530369</v>
+        <v>-8.585349114082366</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.2969753974769906</v>
+        <v>-0.2786370560977889</v>
       </c>
       <c r="F1904" t="n">
         <v>-2.007698752377983</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390426</v>
+        <v>3.763182248390427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.498919493899482</v>
+        <v>-8.453073640451478</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.2486977212776087</v>
+        <v>-0.2303593798984069</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.875423278747097</v>
@@ -45389,10 +45389,10 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.308319819226329</v>
+        <v>-8.262473965778325</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.1696427907207103</v>
+        <v>-0.151304449341509</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.684823604073944</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960985</v>
+        <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.059320020542748</v>
+        <v>-8.013474167094744</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.05713653002361907</v>
+        <v>-0.03879818864441775</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.684823604073944</v>
@@ -45435,10 +45435,10 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.164910010315852</v>
+        <v>-8.119064156867848</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2273484555320797</v>
+        <v>-0.2090101141528784</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.790413593847048</v>
@@ -45458,10 +45458,10 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.183644912434449</v>
+        <v>-8.137799058986445</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1862980745024321</v>
+        <v>-0.1679597331232308</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.79600960350718</v>
@@ -45481,10 +45481,10 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.03570487102685</v>
+        <v>-7.989859017578846</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.2470009806275599</v>
+        <v>-0.2286626392483586</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.775688687598622</v>
@@ -45504,10 +45504,10 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.018546720895555</v>
+        <v>-7.972700867447552</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.2488517068285203</v>
+        <v>-0.230513365449319</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.758530537467328</v>
@@ -45527,10 +45527,10 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.974998314124865</v>
+        <v>-7.929152460676861</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.2383929562153373</v>
+        <v>-0.220054614836136</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.758530537467328</v>
@@ -45550,10 +45550,10 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.732849920671007</v>
+        <v>-7.687004067223003</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1270712444526509</v>
+        <v>-0.1087329030734496</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.758530537467328</v>
@@ -45573,10 +45573,10 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.624590783548485</v>
+        <v>-7.578744930100481</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.08923546914444724</v>
+        <v>-0.07089712776524593</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.758530537467328</v>
@@ -45596,10 +45596,10 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.501299648731354</v>
+        <v>-7.455453795283351</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.04242092120701813</v>
+        <v>-0.02408257982781681</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.635239402650197</v>
@@ -45619,10 +45619,10 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.480150449827911</v>
+        <v>-7.434304596379907</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.02626026340831578</v>
+        <v>-0.007921922029114015</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.614090203746754</v>
@@ -45642,10 +45642,10 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.236385007844467</v>
+        <v>-7.190539154396463</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.06702662173211271</v>
+        <v>0.08536496311131403</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.614090203746754</v>
@@ -45665,10 +45665,10 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.134622187567172</v>
+        <v>-7.088776334119168</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1098560637630466</v>
+        <v>0.1281944051422483</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.600871135354325</v>
@@ -45688,10 +45688,10 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.884771793618097</v>
+        <v>-6.838925940170093</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2025382963263787</v>
+        <v>0.22087663770558</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.600871135354325</v>
@@ -45711,10 +45711,10 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.708879701150664</v>
+        <v>-6.66303384770266</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2764942568340008</v>
+        <v>0.2948325982132021</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.600871135354325</v>
@@ -45734,10 +45734,10 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.537433238128201</v>
+        <v>-6.491587384680197</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.3584003480975397</v>
+        <v>0.3767386894767411</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.429424672331862</v>
@@ -45757,10 +45757,10 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.312400238459378</v>
+        <v>-6.266554385011374</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4474340255813658</v>
+        <v>0.4657723669605671</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.204391672663039</v>
@@ -45780,10 +45780,10 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.248764496225443</v>
+        <v>-6.20291864277744</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4775831235292567</v>
+        <v>0.4959214649084585</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.140755930429105</v>
@@ -45803,10 +45803,10 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.205002314919602</v>
+        <v>-6.159156461471598</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4762822548353891</v>
+        <v>0.4946205962145904</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.140755930429105</v>
@@ -45826,10 +45826,10 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.964571818114742</v>
+        <v>-5.918725964666738</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5741975301822109</v>
+        <v>0.5925358715614122</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.9003254336242443</v>
@@ -45849,10 +45849,10 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.901960469358577</v>
+        <v>-5.846483396495543</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6031713835194967</v>
+        <v>0.6253622126647103</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.9003254336242443</v>
@@ -45872,10 +45872,10 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.848962147077189</v>
+        <v>-5.793485074214155</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6250492963493919</v>
+        <v>0.6472401254946054</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.8449891746223055</v>
@@ -45895,10 +45895,10 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.740157261597462</v>
+        <v>-5.684680188734428</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.6655693217612764</v>
+        <v>0.6877601509064899</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.8449891746223055</v>
@@ -45918,10 +45918,10 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.520136463560451</v>
+        <v>-5.464659390697418</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.7551566779866947</v>
+        <v>0.7773475071319083</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.7037693295543253</v>
@@ -45941,10 +45941,10 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.387268774497174</v>
+        <v>-5.33179170163414</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.824197936413829</v>
+        <v>0.8463887655590425</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.7037693295543253</v>
@@ -45964,10 +45964,10 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.227753670977804</v>
+        <v>-5.17227659811477</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.8891498222618788</v>
+        <v>0.9113406514070923</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.5442542260349553</v>
@@ -45987,10 +45987,10 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-5.083081525878066</v>
+        <v>-5.027604453015033</v>
       </c>
       <c r="E1932" t="n">
-        <v>0.9571067828632138</v>
+        <v>0.9792976120084269</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.3995820809352179</v>
@@ -46010,10 +46010,10 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-5.142956353235759</v>
+        <v>-5.087479280372725</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9191943433215624</v>
+        <v>0.9413851724667759</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.45945690829291</v>
@@ -46033,10 +46033,10 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-5.05615685545675</v>
+        <v>-5.000679782593716</v>
       </c>
       <c r="E1934" t="n">
-        <v>0.976314635755732</v>
+        <v>0.9985054649009457</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.45945690829291</v>
@@ -46056,10 +46056,10 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-5.058626561918556</v>
+        <v>-5.003149489055522</v>
       </c>
       <c r="E1935" t="n">
-        <v>0.9753991545444216</v>
+        <v>0.9975899836896356</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.4619266147547162</v>
@@ -46079,10 +46079,10 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-5.126996748242567</v>
+        <v>-5.071519675379532</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.9590580024895194</v>
+        <v>0.9812488316347334</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.4526509157185012</v>
@@ -46102,10 +46102,10 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.235534929158701</v>
+        <v>-5.180057856295666</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9060794387549573</v>
+        <v>0.9282702679001713</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.4526509157185012</v>
@@ -46125,10 +46125,10 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.266528088487406</v>
+        <v>-5.211051015624371</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.7183917400638622</v>
+        <v>0.7405825692090757</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.4526509157185012</v>
@@ -46148,10 +46148,10 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-5.091053828694937</v>
+        <v>-5.035576755831903</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.7931486759726374</v>
+        <v>0.8153395051178509</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.4526509157185012</v>
@@ -46171,10 +46171,10 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-5.201990081336186</v>
+        <v>-5.146513008473152</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.7245162036773447</v>
+        <v>0.7467070328225587</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.4526509157185012</v>
@@ -46194,10 +46194,10 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.405016658879419</v>
+        <v>-5.349539586016385</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.6464369578799571</v>
+        <v>0.6686277870251707</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.6556774932617346</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264163</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-5.247091059944126</v>
+        <v>-5.191613987081092</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.7197795838862064</v>
+        <v>0.7419704130314204</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.6556774932617346</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-5.160847596917749</v>
+        <v>-5.105370524054714</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.7492232396706182</v>
+        <v>0.7714140688158317</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.6556774932617346</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316047</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-5.206154416316728</v>
+        <v>-5.150677343453694</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.7228762873555516</v>
+        <v>0.7450671165007656</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.6964876562709654</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-5.23518752101903</v>
+        <v>-5.179710448155995</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.7118149185077329</v>
+        <v>0.7340057476529465</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.6964876562709654</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809498</v>
+        <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-5.14237703956817</v>
+        <v>-5.086899966705135</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.6782118029794422</v>
+        <v>0.7004026321246561</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.6036771748201061</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-5.186766508897597</v>
+        <v>-5.131289436034563</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.6623294911722719</v>
+        <v>0.6845203203174859</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.6480666441495337</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472738</v>
+        <v>3.721077195472737</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-5.074095290661347</v>
+        <v>-5.018618217798313</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.7024736869784953</v>
+        <v>0.7246645161237089</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.5353954259132836</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798536</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.961718289478674</v>
+        <v>-4.90624121661564</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.7529157832822315</v>
+        <v>0.7751066124274453</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.5353954259132836</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498864</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-5.159952858365405</v>
+        <v>-5.104475785502371</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.6851191574960782</v>
+        <v>0.7073099866412922</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.7336299948000142</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705325</v>
+        <v>3.643069621705324</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-5.242954139390684</v>
+        <v>-5.18747706652765</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.4902743650866199</v>
+        <v>0.5124651942318339</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.7522008793271879</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.68271631072927</v>
+        <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-5.351568217834015</v>
+        <v>-5.296091144970981</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.5669783944284932</v>
+        <v>0.5891692235737072</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.7522008793271879</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190769</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.438166800815118</v>
+        <v>-5.382689727952084</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.5468519873383748</v>
+        <v>0.5690428164835888</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.7522008793271879</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.399783138256967</v>
+        <v>-5.344306065393932</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.559624893704004</v>
+        <v>0.581815722849218</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.7138172167690368</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532485</v>
+        <v>3.751147197532483</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-5.222666808221801</v>
+        <v>-5.167189735358766</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.6272004545633725</v>
+        <v>0.6493912837085865</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.7138172167690368</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-5.267759053055347</v>
+        <v>-5.212281980192312</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.6098469483918674</v>
+        <v>0.6320377775370809</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.7757132599384265</v>
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011235</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-5.28760851391139</v>
+        <v>-5.032906558953544</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.5956941393558646</v>
+        <v>0.6975749213390023</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.8298857378335189</v>
+        <v>-0.6189365017677079</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.213162526534057</v>
+        <v>2.339732068173543</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71699171898223</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-5.332622727431996</v>
+        <v>-5.077920772474151</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.5584959092792117</v>
+        <v>0.6603766912623494</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.8602346331481235</v>
+        <v>-0.6492853970823125</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.175760644676884</v>
+        <v>2.30233018631637</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509537</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.599627237704431</v>
+        <v>-5.344925282746586</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.4573856675091834</v>
+        <v>0.5592664494923212</v>
       </c>
       <c r="F1959" t="n">
-        <v>-1.054597671191072</v>
+        <v>-0.8436484351252611</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.06483438419006</v>
+        <v>2.191403925829547</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760811</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.700825019141604</v>
+        <v>-5.446123064183759</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.4161104768308155</v>
+        <v>0.5179912588139537</v>
       </c>
       <c r="F1960" t="n">
-        <v>-1.123006484736391</v>
+        <v>-0.9120572486705802</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.02299301795937</v>
+        <v>2.149562559598857</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815456</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.668349432970832</v>
+        <v>-5.413647478012987</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.4267006728534413</v>
+        <v>0.5285814548365795</v>
       </c>
       <c r="F1961" t="n">
-        <v>-1.123006484736391</v>
+        <v>-0.9120572486705802</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.020592979513687</v>
+        <v>2.147162521153174</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378101</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.649311305263534</v>
+        <v>-5.394609350305689</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.430840643144605</v>
+        <v>0.5327214251277432</v>
       </c>
       <c r="F1962" t="n">
-        <v>-1.181190096067586</v>
+        <v>-0.9702408600017748</v>
       </c>
       <c r="G1962" t="n">
-        <v>1.982207531923215</v>
+        <v>2.108777073562702</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.680437936414153</v>
+        <v>-5.425735981456308</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.5959718596230381</v>
+        <v>0.6978526416061763</v>
       </c>
       <c r="F1963" t="n">
-        <v>-1.181190096067586</v>
+        <v>-0.9702408600017748</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.159789400861896</v>
+        <v>2.286358942501382</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067867</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.732758317014945</v>
+        <v>-5.478056362057099</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.5758770363688552</v>
+        <v>0.677757818351993</v>
       </c>
       <c r="F1964" t="n">
-        <v>-1.146243236058713</v>
+        <v>-0.9352939999929026</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.181590845853353</v>
+        <v>2.308160387492839</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789124</v>
+        <v>3.787425580789123</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.753015615543903</v>
+        <v>-5.498313660586057</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.5737826473541978</v>
+        <v>0.675663429337336</v>
       </c>
       <c r="F1965" t="n">
-        <v>-1.146243236058713</v>
+        <v>-0.9352939999929026</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.187599376250279</v>
+        <v>2.314168917889765</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.781501250519908</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.6052726453089</v>
+        <v>-5.350570690351055</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.7120324832402209</v>
+        <v>0.8139132652233587</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.9784358788238302</v>
+        <v>-0.7674866427580195</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.36743643838323</v>
+        <v>2.494005980022717</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181172</v>
+        <v>3.802245929181171</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.707287327840121</v>
+        <v>-5.452585372882276</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.6740202317592132</v>
+        <v>0.7759010137423514</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.9784358788238302</v>
+        <v>-0.7674866427580195</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.370230059914711</v>
+        <v>2.496799601554198</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.80560898539473</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.570677983746029</v>
+        <v>-5.315976028788183</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.7293263177885088</v>
+        <v>0.831207099771647</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.8418265347297378</v>
+        <v>-0.6308772986639271</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.452858014762825</v>
+        <v>2.579427556402312</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890612</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.713443316568679</v>
+        <v>-5.458741361610834</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.6713006613995591</v>
+        <v>0.7731814433826969</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.9845918675523881</v>
+        <v>-0.7736426314865774</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.366279291809345</v>
+        <v>2.492848833448832</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.651145317792556</v>
+        <v>-5.396443362834711</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.7625554147068287</v>
+        <v>0.864436196689967</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.9845918675523881</v>
+        <v>-0.7736426314865774</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.432614845606166</v>
+        <v>2.559184387245653</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992192</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-5.449355120127398</v>
+        <v>-5.194653165169553</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.5518523661622901</v>
+        <v>0.6537331481454278</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.7865736753832338</v>
+        <v>-0.575624439317423</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.260006633297057</v>
+        <v>2.386576174936543</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852424</v>
+        <v>3.841444817852422</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-5.389464438484805</v>
+        <v>-5.13476248352696</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.6460988711415023</v>
+        <v>0.7479796531246405</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.7266829937406403</v>
+        <v>-0.5157337576748295</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.366231274604788</v>
+        <v>2.492800816244275</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319548</v>
+        <v>3.819063300319546</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-5.48720498310978</v>
+        <v>-5.232503028151934</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.6216303894075565</v>
+        <v>0.7235111713906943</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.7425722718736205</v>
+        <v>-0.5316230358078098</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.371325443841044</v>
+        <v>2.49789498548053</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489385</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.663542743232709</v>
+        <v>-5.408840788274864</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.5496312661830562</v>
+        <v>0.6515120481661945</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.91891003199655</v>
+        <v>-0.7079607959307392</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.264058768591958</v>
+        <v>2.390628310231444</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.662853371071486</v>
+        <v>-5.408151416113641</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.5483986330874742</v>
+        <v>0.6502794150706124</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.91891003199655</v>
+        <v>-0.7079607959307392</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.262550386631886</v>
+        <v>2.389119928271373</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024963</v>
+        <v>3.836023391024961</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-5.669424336126078</v>
+        <v>-5.414722381168233</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.5456331145010731</v>
+        <v>0.6475138964842113</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.9254809970511428</v>
+        <v>-0.7145317609853321</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.258470675034566</v>
+        <v>2.385040216674053</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863225</v>
+        <v>3.821591150863223</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-5.661470365831306</v>
+        <v>-5.406768410873461</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.5488147026189822</v>
+        <v>0.65069548460212</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.9254809970511428</v>
+        <v>-0.7145317609853321</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.258470675034566</v>
+        <v>2.385040216674053</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947585</v>
+        <v>3.833040181947583</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-5.651096989498219</v>
+        <v>-5.396395034540374</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.5593458101800217</v>
+        <v>0.6612265921631595</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.9151076207180555</v>
+        <v>-0.7041583846522448</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.271076457862224</v>
+        <v>2.39764599950171</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326877</v>
+        <v>3.822707244326875</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-5.523412679703923</v>
+        <v>-5.268710724746078</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.6153119074724649</v>
+        <v>0.7171926894556031</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.7874233109237591</v>
+        <v>-0.5764740748579483</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.352579417113526</v>
+        <v>2.479148958753013</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314553</v>
+        <v>3.828837911314551</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-5.584079270106312</v>
+        <v>-5.329377315148466</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.5777999437873818</v>
+        <v>0.6796807257705195</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.8691216276422927</v>
+        <v>-0.658172391576482</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.290315099558279</v>
+        <v>2.416884641197765</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690028</v>
+        <v>3.816866067690026</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-5.519085410172666</v>
+        <v>-5.264383455214821</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.6078951903714684</v>
+        <v>0.7097759723546067</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.8422910130381374</v>
+        <v>-0.6313417769723266</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.3105111709314</v>
+        <v>2.437080712570887</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674311</v>
+        <v>3.817961388674309</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-5.619844045929664</v>
+        <v>-5.365142090971819</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.5717526756997473</v>
+        <v>0.6736334576828851</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.9311165817651428</v>
+        <v>-0.7201673456993321</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.261376769326275</v>
+        <v>2.387946310965761</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.82671377916322</v>
+        <v>3.826713779163218</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-5.575641208843764</v>
+        <v>-5.320939253885919</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.5953134130619446</v>
+        <v>0.6971941950450824</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.8869137446792423</v>
+        <v>-0.6759645086134316</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.293778074105652</v>
+        <v>2.420347615745139</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022905</v>
+        <v>3.838228663022903</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-5.612620236507206</v>
+        <v>-5.357918281549361</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.578931802465815</v>
+        <v>0.6808125844489532</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.8499398428879118</v>
+        <v>-0.6389906068221011</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.314372415649698</v>
+        <v>2.440941957289184</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042139</v>
+        <v>3.863924114042137</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-5.632678315372047</v>
+        <v>-5.377976360414202</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.6221563361029183</v>
+        <v>0.7240371180860565</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.8499398428879118</v>
+        <v>-0.6389906068221011</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.365620180832738</v>
+        <v>2.492189722472224</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86536771507828</v>
+        <v>3.865367715078278</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-5.592747642194157</v>
+        <v>-5.338045687236312</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.6365693099683276</v>
+        <v>0.7384500919514658</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.8100091697100215</v>
+        <v>-0.5990599336442107</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.388019289333725</v>
+        <v>2.514588830973212</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232396</v>
+        <v>3.864518876232395</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-5.552277294631452</v>
+        <v>-5.297575339673607</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.6477056772316798</v>
+        <v>0.7495864592148176</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.7695388221473165</v>
+        <v>-0.5585895860815058</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.407249726109618</v>
+        <v>2.533819267749104</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162111</v>
+        <v>3.842576394162109</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-5.487053113504246</v>
+        <v>-5.232351158546401</v>
       </c>
       <c r="E1988" t="n">
-        <v>0.6909827537752666</v>
+        <v>0.7928635357584048</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.7043146410201109</v>
+        <v>-0.4933654049543001</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.463571638878646</v>
+        <v>2.590141180518133</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.463312654099892</v>
+        <v>3.852893538994464</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.829633952372269</v>
+        <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-5.310382276877781</v>
+        <v>-5.283196279112963</v>
       </c>
       <c r="E1989" t="n">
-        <v>0.7051246173074097</v>
+        <v>0.7684864598310606</v>
       </c>
       <c r="F1989" t="n">
-        <v>-0.7166928877733576</v>
+        <v>-0.5381034076659119</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.399618219708255</v>
+        <v>2.559259351190446</v>
       </c>
     </row>
   </sheetData>
